--- a/tables/autoencoder_per_event_metrics.xlsx
+++ b/tables/autoencoder_per_event_metrics.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H92"/>
+  <dimension ref="A1:H89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,14 +461,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>burning the workpiece for 30 seconds</t>
+          <t>drilling the workpiece for 2 seconds</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>256</v>
+        <v>20</v>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 20 seconds</t>
+          <t>moving towards the slot 8</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -529,14 +529,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 2 seconds</t>
+          <t>dropping off the workpiece at the drilling machine sink</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -563,21 +563,21 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 21 seconds</t>
+          <t>burning the workpiece for 30 seconds</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>256</v>
       </c>
       <c r="C5" t="n">
+        <v>13</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
         <v>1</v>
       </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>1.000</t>
@@ -585,33 +585,33 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.929</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.963</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 16 seconds</t>
+          <t>moving towards the slot 6</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>110</v>
       </c>
       <c r="C6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
         <v>1</v>
       </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>1.000</t>
@@ -619,32 +619,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.857</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.923</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 15 seconds</t>
+          <t>burning the workpiece for 15 seconds</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26</v>
+        <v>451</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -653,12 +653,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.852</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.920</t>
         </is>
       </c>
     </row>
@@ -672,13 +672,13 @@
         <v>516</v>
       </c>
       <c r="C8" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -687,32 +687,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.955</t>
+          <t>0.821</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.977</t>
+          <t>0.902</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>burning the workpiece for 15 seconds</t>
+          <t>milling the workpiece</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>451</v>
+        <v>106</v>
       </c>
       <c r="C9" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -721,284 +721,284 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.862</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.926</t>
+          <t>0.857</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>milling the workpiece</t>
+          <t>temper the workpiece for 40 seconds</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>106</v>
+        <v>1346</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.883</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>0.803</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.889</t>
+          <t>0.841</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>moving towards the slot 6</t>
+          <t>opening the oven door</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>110</v>
+        <v>867</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>0.919</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.756</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.889</t>
+          <t>0.829</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the oven</t>
+          <t>transporting the workpiece to the light barrier 3</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>82</v>
+        <v>404</v>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.706</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.889</t>
+          <t>0.828</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the oven</t>
+          <t>moving towards the oven</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1201</v>
+        <v>2451</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E13" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.938</t>
+          <t>0.801</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.804</t>
+          <t>0.830</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.865</t>
+          <t>0.815</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the sink 3</t>
+          <t>transporting the workpiece to the milling_machine</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>45</v>
+        <v>2519</v>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>96</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.821</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.800</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>0.810</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 6</t>
+          <t>picking up the workpiece from the punching machine sink</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>193</v>
+        <v>83</v>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.833</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.833</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.833</t>
+          <t>0.800</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>temper the workpiece for 40 seconds</t>
+          <t>transporting the bucket to the slot 7</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1346</v>
+        <v>143</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E16" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.881</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.776</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.825</t>
+          <t>0.800</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>moving towards the slot 2</t>
+          <t>transporting the workpiece to the sorting machine</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>95</v>
+        <v>1029</v>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.875</t>
+          <t>0.974</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.778</t>
+          <t>0.661</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.824</t>
+          <t>0.787</t>
         </is>
       </c>
     </row>
@@ -1015,44 +1015,44 @@
         <v>20</v>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.870</t>
+          <t>0.833</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.769</t>
+          <t>0.741</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.816</t>
+          <t>0.784</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the drilling machine sink</t>
+          <t>picking up the workpiece from the high bay warehouse</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1297</v>
+        <v>360</v>
       </c>
       <c r="C19" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1061,305 +1061,305 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.672</t>
+          <t>0.636</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.804</t>
+          <t>0.778</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 4</t>
+          <t>picking up the workpiece from the human workstation</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>158</v>
+        <v>194</v>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.636</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>0.778</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the sorting machine</t>
+          <t>transporting the workpiece to the punch or drill</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1029</v>
+        <v>746</v>
       </c>
       <c r="C21" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>17</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.972</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.673</t>
+          <t>0.622</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.795</t>
+          <t>0.767</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the milling_machine</t>
+          <t>transporting the workpiece to the drilling machine sink</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2519</v>
+        <v>1297</v>
       </c>
       <c r="C22" t="n">
-        <v>94</v>
+        <v>38</v>
       </c>
       <c r="D22" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.825</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.764</t>
+          <t>0.613</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.793</t>
+          <t>0.760</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>moving towards the oven</t>
+          <t>picking up the workpiece from the oven</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2451</v>
+        <v>1201</v>
       </c>
       <c r="C23" t="n">
-        <v>109</v>
+        <v>34</v>
       </c>
       <c r="D23" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.779</t>
+          <t>0.919</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.807</t>
+          <t>0.642</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.793</t>
+          <t>0.756</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the high bay warehouse</t>
+          <t>transporting the workpiece to the mill</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>360</v>
+        <v>217</v>
       </c>
       <c r="C24" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.900</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.647</t>
+          <t>0.643</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.786</t>
+          <t>0.750</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>opening the oven door</t>
+          <t>moving towards the slot 3</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>867</v>
+        <v>139</v>
       </c>
       <c r="C25" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="D25" t="n">
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.897</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.650</t>
+          <t>0.857</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.754</t>
+          <t>0.750</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the mill</t>
+          <t>moving towards the slot 5</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>217</v>
+        <v>71</v>
       </c>
       <c r="C26" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0.900</t>
+          <t>0.571</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.643</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.727</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the sink 3</t>
+          <t>picking up the workpiece from the sink 2</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="C27" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" t="n">
         <v>3</v>
       </c>
-      <c r="D27" t="n">
-        <v>0</v>
-      </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
+          <t>0.571</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
           <t>1.000</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>0.600</t>
-        </is>
-      </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.727</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>moving towards the slot 8</t>
+          <t>picking up the workpiece from the high bay warehouse waiting platform</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>72</v>
+        <v>150</v>
       </c>
       <c r="C28" t="n">
+        <v>4</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
         <v>3</v>
       </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="n">
-        <v>2</v>
-      </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>1.000</t>
@@ -1367,381 +1367,381 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>0.571</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.727</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 3 seconds</t>
+          <t>transporting the workpiece to the drill</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>43</v>
+        <v>242</v>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D29" t="n">
         <v>2</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>0.818</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.643</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.720</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the high bay warehouse</t>
+          <t>moving towards the slot 1</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="C30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>0.833</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.875</t>
+          <t>0.625</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.737</t>
+          <t>0.714</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the punch or drill</t>
+          <t>transporting the bucket to the slot 5</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>746</v>
+        <v>101</v>
       </c>
       <c r="C31" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.625</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.579</t>
+          <t>0.833</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.733</t>
+          <t>0.714</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the oven</t>
+          <t>transporting the bucket to the slot 4</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1627</v>
+        <v>158</v>
       </c>
       <c r="C32" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="D32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" t="n">
         <v>1</v>
       </c>
-      <c r="E32" t="n">
-        <v>36</v>
-      </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.980</t>
+          <t>0.625</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>0.833</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.722</t>
+          <t>0.714</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the human workstation</t>
+          <t>transporting the workpiece to the oven</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>194</v>
+        <v>1627</v>
       </c>
       <c r="C33" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.979</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.562</t>
+          <t>0.529</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.720</t>
+          <t>0.687</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 3</t>
+          <t>drilling the workpiece for 24 seconds</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>257</v>
+        <v>26</v>
       </c>
       <c r="C34" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.714</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.714</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.714</t>
+          <t>0.667</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 7</t>
+          <t>transporting the workpiece to the initial position</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="C35" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.706</t>
+          <t>0.667</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the light barrier 3</t>
+          <t>transporting the bucket to the slot 1</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>404</v>
+        <v>326</v>
       </c>
       <c r="C36" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E36" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.737</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.542</t>
+          <t>0.609</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.703</t>
+          <t>0.667</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the outside of the oven</t>
+          <t>transporting the workpiece to the sink 3</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>522</v>
+        <v>77</v>
       </c>
       <c r="C37" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.564</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.880</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.688</t>
+          <t>0.667</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>transporting the bucket to the high-bay warehouse crane jib</t>
+          <t>transporting the bucket to the slot 6</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>907</v>
+        <v>193</v>
       </c>
       <c r="C38" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="D38" t="n">
         <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.931</t>
+          <t>0.714</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0.529</t>
+          <t>0.625</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.675</t>
+          <t>0.667</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the dm_2_sink</t>
+          <t>picking up the bucket from the slot</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>97</v>
+        <v>1868</v>
       </c>
       <c r="C39" t="n">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="D39" t="n">
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.833</t>
+          <t>0.980</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.556</t>
+          <t>0.505</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1760,456 +1760,456 @@
         <v>474</v>
       </c>
       <c r="C40" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D40" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0.576</t>
+          <t>0.536</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.792</t>
+          <t>0.833</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.652</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>lowering the workpiece</t>
+          <t>transporting the bucket to the slot 0</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>38</v>
+        <v>652</v>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.733</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.579</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.647</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 28 seconds</t>
+          <t>dropping off the bucket at the slot</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>12</v>
+        <v>2069</v>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.957</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.478</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.638</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the sink 2</t>
+          <t>transporting the bucket to the high-bay warehouse crane jib</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>70</v>
+        <v>907</v>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.913</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.488</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.636</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 2</t>
+          <t>picking up the bucket from the conveyor belt</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>124</v>
+        <v>1832</v>
       </c>
       <c r="C44" t="n">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="D44" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E44" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.812</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.619</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 35 seconds</t>
+          <t>UNKNOWN_EVENT</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>22</v>
+        <v>8244</v>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>220</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>196</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.738</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.529</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.616</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>picking up the bucket from the conveyor belt</t>
+          <t>transporting the bucket to the slot 3</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1832</v>
+        <v>257</v>
       </c>
       <c r="C46" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="D46" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E46" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0.842</t>
+          <t>0.600</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>0.539</t>
+          <t>0.600</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>0.658</t>
+          <t>0.600</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>calibrating motor 3</t>
+          <t>transporting the workpiece to the dm_2_sink</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>5003</v>
+        <v>97</v>
       </c>
       <c r="C47" t="n">
-        <v>137</v>
+        <v>3</v>
       </c>
       <c r="D47" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>117</v>
+        <v>3</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0.830</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>0.539</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>0.654</t>
+          <t>0.600</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>UNKNOWN_EVENT</t>
+          <t>moving towards the slot 2</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>8244</v>
+        <v>95</v>
       </c>
       <c r="C48" t="n">
-        <v>242</v>
+        <v>3</v>
       </c>
       <c r="D48" t="n">
-        <v>77</v>
+        <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>181</v>
+        <v>2</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>0.759</t>
+          <t>0.600</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>0.572</t>
+          <t>0.600</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>0.652</t>
+          <t>0.600</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 1</t>
+          <t>dropping off the workpiece at the high bay warehouse</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>326</v>
+        <v>38</v>
       </c>
       <c r="C49" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D49" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E49" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0.688</t>
+          <t>0.600</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>0.611</t>
+          <t>0.600</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0.647</t>
+          <t>0.600</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the drilling machine sink</t>
+          <t>transporting the workpiece to the punch</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>296</v>
+        <v>350</v>
       </c>
       <c r="C50" t="n">
+        <v>11</v>
+      </c>
+      <c r="D50" t="n">
+        <v>8</v>
+      </c>
+      <c r="E50" t="n">
         <v>7</v>
       </c>
-      <c r="D50" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" t="n">
-        <v>8</v>
-      </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.579</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>0.467</t>
+          <t>0.611</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>0.595</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>picking up the bucket from the slot</t>
+          <t>moving towards the slot 0</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1868</v>
+        <v>551</v>
       </c>
       <c r="C51" t="n">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E51" t="n">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>0.977</t>
+          <t>0.800</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0.457</t>
+          <t>0.462</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0.623</t>
+          <t>0.585</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 0</t>
+          <t>calibrating motor 3</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>652</v>
+        <v>5003</v>
       </c>
       <c r="C52" t="n">
-        <v>22</v>
+        <v>120</v>
       </c>
       <c r="D52" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="E52" t="n">
-        <v>19</v>
+        <v>150</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>0.733</t>
+          <t>0.805</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>0.537</t>
+          <t>0.444</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>0.620</t>
+          <t>0.573</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the drill</t>
+          <t>dropping off the workpiece at the oven</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>242</v>
+        <v>82</v>
       </c>
       <c r="C53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" t="n">
         <v>2</v>
       </c>
-      <c r="E53" t="n">
-        <v>3</v>
-      </c>
       <c r="F53" t="inlineStr">
         <is>
           <t>0.667</t>
@@ -2217,250 +2217,250 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
           <t>0.571</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>0.615</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>moving towards the slot 3</t>
+          <t>transporting the workpiece to the pm_1_sink</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>139</v>
+        <v>91</v>
       </c>
       <c r="C54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D54" t="n">
         <v>4</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>0.429</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>0.571</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>moving towards the slot 0</t>
+          <t>moving towards the slot 4</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>551</v>
+        <v>65</v>
       </c>
       <c r="C55" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D55" t="n">
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>0.824</t>
+          <t>0.571</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>0.467</t>
+          <t>0.571</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>0.596</t>
+          <t>0.571</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>transporting the bucket to the conveyor belt</t>
+          <t>transporting the workpiece to the outside of the oven</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2376</v>
+        <v>522</v>
       </c>
       <c r="C56" t="n">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="D56" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>0.725</t>
+          <t>0.444</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>0.485</t>
+          <t>0.762</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>0.581</t>
+          <t>0.561</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>dropping off the bucket at the slot</t>
+          <t>transporting the bucket to the high bay warehouse crane jib</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2069</v>
+        <v>159</v>
       </c>
       <c r="C57" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="D57" t="n">
+        <v>9</v>
+      </c>
+      <c r="E57" t="n">
         <v>2</v>
       </c>
-      <c r="E57" t="n">
-        <v>60</v>
-      </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0.956</t>
+          <t>0.438</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>0.417</t>
+          <t>0.778</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>0.581</t>
+          <t>0.560</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ejecting the workpiece to the sink 2</t>
+          <t>transporting the bucket to the conveyor belt</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>27</v>
+        <v>2376</v>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="D58" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.730</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.446</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>0.554</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the high bay warehouse waiting platform</t>
+          <t>moving towards the sink 2</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>150</v>
+        <v>245</v>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E59" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.571</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>0.533</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>moving towards the sink 2</t>
+          <t>transporting the bucket to the slot 8</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>245</v>
+        <v>100</v>
       </c>
       <c r="C60" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D60" t="n">
         <v>6</v>
       </c>
       <c r="E60" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.400</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>0.800</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>0.533</t>
         </is>
       </c>
     </row>
@@ -2474,124 +2474,124 @@
         <v>110</v>
       </c>
       <c r="C61" t="n">
+        <v>4</v>
+      </c>
+      <c r="D61" t="n">
         <v>3</v>
       </c>
-      <c r="D61" t="n">
+      <c r="E61" t="n">
         <v>4</v>
       </c>
-      <c r="E61" t="n">
-        <v>1</v>
-      </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>0.429</t>
+          <t>0.571</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>0.533</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>calibrating motor 2</t>
+          <t>transporting the workpiece to the human workstation</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2036</v>
+        <v>924</v>
       </c>
       <c r="C62" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="D62" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E62" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>0.577</t>
+          <t>0.773</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>0.466</t>
+          <t>0.386</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>0.516</t>
+          <t>0.515</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 24 seconds</t>
+          <t>calibrating motor 2</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>26</v>
+        <v>2036</v>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="E63" t="n">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.597</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.447</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.511</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 8</t>
+          <t>picking up the workpiece from the sink 3</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="C64" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2603,29 +2603,29 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the drilling machine sink</t>
+          <t>transporting the bucket to the slot 2</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>53</v>
+        <v>124</v>
       </c>
       <c r="C65" t="n">
+        <v>2</v>
+      </c>
+      <c r="D65" t="n">
+        <v>3</v>
+      </c>
+      <c r="E65" t="n">
         <v>1</v>
       </c>
-      <c r="D65" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" t="n">
-        <v>2</v>
-      </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.400</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -2637,29 +2637,29 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the punching machine sink</t>
+          <t>drilling the workpiece for 3 seconds</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="C66" t="n">
         <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
           <t>1.000</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>0.333</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -2671,29 +2671,29 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the punch</t>
+          <t>picking up the workpiece from the drilling machine sink</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>350</v>
+        <v>296</v>
       </c>
       <c r="C67" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D67" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>0.538</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>0.467</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -2705,632 +2705,632 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ejecting the workpiece to the conveyor belt</t>
+          <t>moving towards the sink 3</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>113</v>
+        <v>191</v>
       </c>
       <c r="C68" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D68" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E68" t="n">
         <v>1</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.304</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>0.875</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>0.471</t>
+          <t>0.452</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>transporting the bucket to the high bay warehouse crane jib</t>
+          <t>transporting the workpiece to the high bay warehouse waiting platform</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>159</v>
+        <v>191</v>
       </c>
       <c r="C69" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D69" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>0.444</t>
+          <t>0.429</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>moving towards the slot 5</t>
+          <t>transporting the bucket to the vacuum gripper robot crane jib</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>71</v>
+        <v>270</v>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D70" t="n">
+        <v>28</v>
+      </c>
+      <c r="E70" t="n">
         <v>3</v>
       </c>
-      <c r="E70" t="n">
-        <v>2</v>
-      </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.282</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.786</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>0.444</t>
+          <t>0.415</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the sink 2</t>
+          <t>transporting the workpiece to the sink 2</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="C71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E71" t="n">
         <v>2</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
           <t>0.400</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>0.500</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>0.444</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>moving towards the slot 1</t>
+          <t>transporting the workpiece to the high bay warehouse</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="C72" t="n">
         <v>2</v>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E72" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>0.444</t>
+          <t>0.400</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the human workstation</t>
+          <t>dropping off the workpiece at the high bay warehouse waiting platform</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>924</v>
+        <v>46</v>
       </c>
       <c r="C73" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D73" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E73" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>0.722</t>
+          <t>0.200</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>0.302</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>0.426</t>
+          <t>0.333</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>moving towards the sink 3</t>
+          <t>transporting the workpiece to the sorting machine conveyor belt</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>191</v>
+        <v>50</v>
       </c>
       <c r="C74" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D74" t="n">
         <v>14</v>
       </c>
       <c r="E74" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.176</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>0.583</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>0.424</t>
+          <t>0.300</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the initial position</t>
+          <t>ejecting the workpiece to the sink 3</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>71</v>
+        <v>29</v>
       </c>
       <c r="C75" t="n">
         <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.143</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.250</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ejecting the workpiece to the sink 3</t>
+          <t>ejecting the workpiece to the conveyor belt</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>29</v>
+        <v>113</v>
       </c>
       <c r="C76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.100</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>0.364</t>
+          <t>0.182</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>transporting the bucket to the vacuum gripper robot crane jib</t>
+          <t>moving towards the slot 7</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>270</v>
+        <v>50</v>
       </c>
       <c r="C77" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E77" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>0.225</t>
+          <t>0.062</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>0.692</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>0.340</t>
+          <t>0.118</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the high bay warehouse</t>
+          <t>ejecting the workpiece to the sink 1</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>moving towards the slot 4</t>
+          <t>drilling the workpiece for 28 seconds</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="C79" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" t="n">
         <v>1</v>
       </c>
-      <c r="D79" t="n">
-        <v>3</v>
-      </c>
       <c r="E79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the high bay warehouse waiting platform</t>
+          <t>moving towards the punching machine sink</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>191</v>
+        <v>3</v>
       </c>
       <c r="C80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E80" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 5</t>
+          <t>drilling the workpiece for 15 seconds</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>101</v>
+        <v>26</v>
       </c>
       <c r="C81" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" t="n">
         <v>1</v>
       </c>
-      <c r="D81" t="n">
-        <v>3</v>
-      </c>
-      <c r="E81" t="n">
-        <v>3</v>
-      </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the pm_1_sink</t>
+          <t>drilling the workpiece for 4 seconds</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>91</v>
+        <v>2</v>
       </c>
       <c r="C82" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" t="n">
         <v>1</v>
       </c>
-      <c r="D82" t="n">
-        <v>4</v>
-      </c>
-      <c r="E82" t="n">
-        <v>3</v>
-      </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>0.200</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>moving towards the slot 7</t>
+          <t>ejecting the workpiece to the sink 2</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="C83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>0.211</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the sorting machine conveyor belt</t>
+          <t>drilling the workpiece for 35 seconds</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="C84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>moving towards the sink 1</t>
+          <t>dropping off the workpiece at the human workstation</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="E85" t="n">
         <v>0</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>0.080</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the sink 1</t>
+          <t>moving towards the sink 1</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -3351,20 +3351,20 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the sorting machine conveyor belt</t>
+          <t>drilling the workpiece for 20 seconds</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>moving towards the punching machine sink</t>
+          <t>dropping off the workpiece at the sorting machine conveyor belt</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -3419,17 +3419,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the high bay warehouse waiting platform</t>
+          <t>lowering the workpiece</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
         <v>2</v>
@@ -3445,108 +3445,6 @@
         </is>
       </c>
       <c r="H89" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>drilling the workpiece for 4 seconds</t>
-        </is>
-      </c>
-      <c r="B90" t="n">
-        <v>2</v>
-      </c>
-      <c r="C90" t="n">
-        <v>0</v>
-      </c>
-      <c r="D90" t="n">
-        <v>0</v>
-      </c>
-      <c r="E90" t="n">
-        <v>1</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>ejecting the workpiece to the sink 1</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>4</v>
-      </c>
-      <c r="C91" t="n">
-        <v>0</v>
-      </c>
-      <c r="D91" t="n">
-        <v>4</v>
-      </c>
-      <c r="E91" t="n">
-        <v>0</v>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>dropping off the workpiece at the human workstation</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
-        <v>53</v>
-      </c>
-      <c r="C92" t="n">
-        <v>0</v>
-      </c>
-      <c r="D92" t="n">
-        <v>2</v>
-      </c>
-      <c r="E92" t="n">
-        <v>4</v>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
         <is>
           <t>0.000</t>
         </is>

--- a/tables/autoencoder_per_event_metrics.xlsx
+++ b/tables/autoencoder_per_event_metrics.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H89"/>
+  <dimension ref="A1:H86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,14 +461,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 2 seconds</t>
+          <t>drilling the workpiece for 35 seconds</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>moving towards the slot 8</t>
+          <t>drilling the workpiece for 24 seconds</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -529,14 +529,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the drilling machine sink</t>
+          <t>milling the workpiece</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>53</v>
+        <v>106</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -563,20 +563,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>burning the workpiece for 30 seconds</t>
+          <t>moving towards the slot 8</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>256</v>
+        <v>72</v>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -585,32 +585,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.929</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.963</t>
+          <t>1.000</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>moving towards the slot 6</t>
+          <t>moving towards the slot 4</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -619,32 +619,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.923</t>
+          <t>1.000</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>burning the workpiece for 15 seconds</t>
+          <t>dropping off the workpiece at the oven</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>451</v>
+        <v>82</v>
       </c>
       <c r="C7" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -653,32 +653,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.852</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.920</t>
+          <t>1.000</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>burning the workpiece for 25 seconds</t>
+          <t>drilling the workpiece for 15 seconds</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>516</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -687,23 +687,23 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.821</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.902</t>
+          <t>1.000</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>milling the workpiece</t>
+          <t>moving towards the slot 3</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="C9" t="n">
         <v>3</v>
@@ -712,7 +712,7 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -721,100 +721,100 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>1.000</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>temper the workpiece for 40 seconds</t>
+          <t>lowering the workpiece</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1346</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.883</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.803</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.841</t>
+          <t>1.000</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>opening the oven door</t>
+          <t>drilling the workpiece for 20 seconds</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>867</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.919</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.756</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.829</t>
+          <t>1.000</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the light barrier 3</t>
+          <t>burning the workpiece for 25 seconds</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>404</v>
+        <v>516</v>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -823,131 +823,131 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.706</t>
+          <t>0.800</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.828</t>
+          <t>0.889</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>moving towards the oven</t>
+          <t>moving towards the sink 2</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2451</v>
+        <v>244</v>
       </c>
       <c r="C13" t="n">
-        <v>117</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.801</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.830</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.815</t>
+          <t>0.857</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the milling_machine</t>
+          <t>burning the workpiece for 20 seconds</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2519</v>
+        <v>534</v>
       </c>
       <c r="C14" t="n">
-        <v>96</v>
+        <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.821</t>
+          <t>0.765</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>0.929</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.810</t>
+          <t>0.839</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the punching machine sink</t>
+          <t>transporting the workpiece to the milling_machine</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>83</v>
+        <v>2518</v>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.805</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.805</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>0.805</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 7</t>
+          <t>transporting the workpiece to the pm_1_sink</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>143</v>
+        <v>91</v>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -971,88 +971,88 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the sorting machine</t>
+          <t>temper the workpiece for 40 seconds</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1029</v>
+        <v>1346</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E17" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.974</t>
+          <t>0.821</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.661</t>
+          <t>0.719</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.787</t>
+          <t>0.767</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>burning the workpiece for 20 seconds</t>
+          <t>transporting the workpiece to the punch or drill</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>534</v>
+        <v>746</v>
       </c>
       <c r="C18" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.833</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.741</t>
+          <t>0.619</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.784</t>
+          <t>0.765</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the high bay warehouse</t>
+          <t>burning the workpiece for 15 seconds</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>360</v>
+        <v>451</v>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1061,66 +1061,66 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>0.615</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.778</t>
+          <t>0.762</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the human workstation</t>
+          <t>transporting the bucket to the slot 4</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>194</v>
+        <v>158</v>
       </c>
       <c r="C20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>0.857</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.778</t>
+          <t>0.750</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the punch or drill</t>
+          <t>opening the oven door</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>746</v>
+        <v>867</v>
       </c>
       <c r="C21" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1129,134 +1129,134 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.622</t>
+          <t>0.579</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.767</t>
+          <t>0.733</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the drilling machine sink</t>
+          <t>UNKNOWN_EVENT</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1297</v>
+        <v>8244</v>
       </c>
       <c r="C22" t="n">
-        <v>38</v>
+        <v>138</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="E22" t="n">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.798</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.613</t>
+          <t>0.670</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.760</t>
+          <t>0.728</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the oven</t>
+          <t>dropping off the bucket at the slot</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1201</v>
+        <v>2069</v>
       </c>
       <c r="C23" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.919</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.642</t>
+          <t>0.551</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.756</t>
+          <t>0.711</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the mill</t>
+          <t>transporting the workpiece to the drilling machine sink</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>217</v>
+        <v>1297</v>
       </c>
       <c r="C24" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.900</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.643</t>
+          <t>0.548</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.708</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>moving towards the slot 3</t>
+          <t>transporting the workpiece to the inside of the oven</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>139</v>
+        <v>474</v>
       </c>
       <c r="C25" t="n">
+        <v>12</v>
+      </c>
+      <c r="D25" t="n">
         <v>6</v>
       </c>
-      <c r="D25" t="n">
-        <v>3</v>
-      </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1265,196 +1265,196 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.706</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>moving towards the slot 5</t>
+          <t>transporting the bucket to the slot 1</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>71</v>
+        <v>326</v>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>0.600</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.857</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.727</t>
+          <t>0.706</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the sink 2</t>
+          <t>moving towards the oven</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>59</v>
+        <v>2451</v>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>0.755</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.649</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.727</t>
+          <t>0.698</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the high bay warehouse waiting platform</t>
+          <t>transporting the bucket to the high-bay warehouse crane jib</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>150</v>
+        <v>907</v>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.867</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>0.565</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.727</t>
+          <t>0.684</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the drill</t>
+          <t>transporting the workpiece to the sink 2</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>242</v>
+        <v>70</v>
       </c>
       <c r="C29" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0.818</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.643</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>0.720</t>
+          <t>0.667</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>moving towards the slot 1</t>
+          <t>burning the workpiece for 30 seconds</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>163</v>
+        <v>256</v>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.833</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.625</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.714</t>
+          <t>0.667</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 5</t>
+          <t>transporting the workpiece to the high bay warehouse</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>101</v>
+        <v>173</v>
       </c>
       <c r="C31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D31" t="n">
         <v>3</v>
@@ -1464,207 +1464,207 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.625</t>
+          <t>0.571</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.833</t>
+          <t>0.800</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.714</t>
+          <t>0.667</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 4</t>
+          <t>picking up the workpiece from the high bay warehouse waiting platform</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.625</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.833</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.714</t>
+          <t>0.667</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the oven</t>
+          <t>picking up the bucket from the slot</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1627</v>
+        <v>1868</v>
       </c>
       <c r="C33" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.979</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.529</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.687</t>
+          <t>0.667</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 24 seconds</t>
+          <t>transporting the workpiece to the oven</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>26</v>
+        <v>1627</v>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.952</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.488</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.645</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the initial position</t>
+          <t>picking up the workpiece from the oven</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>71</v>
+        <v>1202</v>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.650</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.619</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.634</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 1</t>
+          <t>picking up the bucket from the conveyor belt</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>326</v>
+        <v>1832</v>
       </c>
       <c r="C36" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E36" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.737</t>
+          <t>0.840</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.609</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.627</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the sink 3</t>
+          <t>picking up the workpiece from the high bay warehouse</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>77</v>
+        <v>360</v>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1673,240 +1673,240 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.455</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.625</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 6</t>
+          <t>transporting the workpiece to the human workstation</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>193</v>
+        <v>924</v>
       </c>
       <c r="C38" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E38" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.714</t>
+          <t>0.765</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0.625</t>
+          <t>0.520</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.619</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>picking up the bucket from the slot</t>
+          <t>transporting the bucket to the conveyor belt</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1868</v>
+        <v>2376</v>
       </c>
       <c r="C39" t="n">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E39" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.980</t>
+          <t>0.900</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.505</t>
+          <t>0.458</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.607</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the inside of the oven</t>
+          <t>calibrating motor 3</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>474</v>
+        <v>5003</v>
       </c>
       <c r="C40" t="n">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="D40" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E40" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0.536</t>
+          <t>0.808</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.833</t>
+          <t>0.480</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0.652</t>
+          <t>0.602</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 0</t>
+          <t>transporting the workpiece to the sorting machine</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>652</v>
+        <v>1029</v>
       </c>
       <c r="C41" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D41" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0.733</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.579</t>
+          <t>0.406</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.647</t>
+          <t>0.578</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>dropping off the bucket at the slot</t>
+          <t>transporting the bucket to the slot 8</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2069</v>
+        <v>100</v>
       </c>
       <c r="C42" t="n">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E42" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.957</t>
+          <t>0.400</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.478</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.638</t>
+          <t>0.571</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>transporting the bucket to the high-bay warehouse crane jib</t>
+          <t>transporting the workpiece to the dm_2_sink</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>907</v>
+        <v>97</v>
       </c>
       <c r="C43" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.913</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.488</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>0.571</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>picking up the bucket from the conveyor belt</t>
+          <t>transporting the workpiece to the mill</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1832</v>
+        <v>217</v>
       </c>
       <c r="C44" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.812</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1916,575 +1916,575 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.619</t>
+          <t>0.571</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>UNKNOWN_EVENT</t>
+          <t>transporting the bucket to the slot 6</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>8244</v>
+        <v>193</v>
       </c>
       <c r="C45" t="n">
-        <v>220</v>
+        <v>2</v>
       </c>
       <c r="D45" t="n">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>196</v>
+        <v>2</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.738</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.529</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.616</t>
+          <t>0.571</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 3</t>
+          <t>transporting the bucket to the slot 5</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>257</v>
+        <v>101</v>
       </c>
       <c r="C46" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>0.400</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>0.571</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the dm_2_sink</t>
+          <t>transporting the bucket to the slot 0</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>97</v>
+        <v>652</v>
       </c>
       <c r="C47" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E47" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.571</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.571</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>0.571</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>moving towards the slot 2</t>
+          <t>moving towards the slot 0</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>95</v>
+        <v>551</v>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>0.889</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>0.381</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>0.533</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the high bay warehouse</t>
+          <t>transporting the workpiece to the outside of the oven</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>38</v>
+        <v>522</v>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D49" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>0.429</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>0.522</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the punch</t>
+          <t>moving towards the slot 2</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>350</v>
+        <v>95</v>
       </c>
       <c r="C50" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>0.579</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>0.611</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>0.595</t>
+          <t>0.500</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>moving towards the slot 0</t>
+          <t>dropping off the workpiece at the high bay warehouse</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>551</v>
+        <v>38</v>
       </c>
       <c r="C51" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0.462</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0.585</t>
+          <t>0.500</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>calibrating motor 3</t>
+          <t>ejecting the workpiece to the sink 2</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>5003</v>
+        <v>27</v>
       </c>
       <c r="C52" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>150</v>
+        <v>1</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>0.805</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>0.444</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>0.573</t>
+          <t>0.500</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the oven</t>
+          <t>picking up the workpiece from the drilling machine sink</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>82</v>
+        <v>296</v>
       </c>
       <c r="C53" t="n">
         <v>2</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
           <t>0.500</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>0.571</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the pm_1_sink</t>
+          <t>dropping off the workpiece at the human workstation</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>91</v>
+        <v>53</v>
       </c>
       <c r="C54" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E54" t="n">
         <v>2</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
           <t>0.500</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>0.667</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>0.571</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>moving towards the slot 4</t>
+          <t>calibrating motor 2</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>65</v>
+        <v>2036</v>
       </c>
       <c r="C55" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D55" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E55" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>0.720</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>0.327</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>0.450</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the outside of the oven</t>
+          <t>transporting the bucket to the slot 2</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>522</v>
+        <v>124</v>
       </c>
       <c r="C56" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D56" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
+          <t>0.400</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
           <t>0.444</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>0.762</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>0.561</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>transporting the bucket to the high bay warehouse crane jib</t>
+          <t>transporting the workpiece to the light barrier 3</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>159</v>
+        <v>404</v>
       </c>
       <c r="C57" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D57" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0.438</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>0.778</t>
+          <t>0.273</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>0.560</t>
+          <t>0.429</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>transporting the bucket to the conveyor belt</t>
+          <t>transporting the bucket to the slot 3</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2376</v>
+        <v>257</v>
       </c>
       <c r="C58" t="n">
-        <v>54</v>
+        <v>3</v>
       </c>
       <c r="D58" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>67</v>
+        <v>5</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>0.730</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>0.446</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>0.554</t>
+          <t>0.429</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>moving towards the sink 2</t>
+          <t>transporting the bucket to the vacuum gripper robot crane jib</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="C59" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D59" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E59" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>0.286</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.857</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>0.533</t>
+          <t>0.429</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 8</t>
+          <t>transporting the workpiece to the punch</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="C60" t="n">
         <v>4</v>
       </c>
       <c r="D60" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E60" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>0.364</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>0.533</t>
+          <t>0.421</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the ejection position</t>
+          <t>transporting the workpiece to the high bay warehouse waiting platform</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>110</v>
+        <v>191</v>
       </c>
       <c r="C61" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D61" t="n">
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>0.250</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2494,167 +2494,167 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>0.533</t>
+          <t>0.333</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the human workstation</t>
+          <t>ejecting the workpiece to the conveyor belt</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>924</v>
+        <v>113</v>
       </c>
       <c r="C62" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E62" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>0.773</t>
+          <t>0.250</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>0.386</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>0.515</t>
+          <t>0.286</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>calibrating motor 2</t>
+          <t>transporting the bucket to the high bay warehouse crane jib</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2036</v>
+        <v>159</v>
       </c>
       <c r="C63" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="E63" t="n">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>0.597</t>
+          <t>0.250</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>0.447</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>0.511</t>
+          <t>0.286</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the sink 3</t>
+          <t>transporting the workpiece to the drill</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>45</v>
+        <v>242</v>
       </c>
       <c r="C64" t="n">
         <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.167</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.286</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 2</t>
+          <t>moving towards the sink 3</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>124</v>
+        <v>190</v>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.100</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.200</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.133</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 3 seconds</t>
+          <t>moving towards the sink 1</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C66" t="n">
         <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="E66" t="n">
         <v>0</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.045</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2664,398 +2664,398 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.087</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the drilling machine sink</t>
+          <t>transporting the workpiece to the sorting machine conveyor belt</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>296</v>
+        <v>50</v>
       </c>
       <c r="C67" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E67" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>moving towards the sink 3</t>
+          <t>moving towards the slot 6</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>191</v>
+        <v>110</v>
       </c>
       <c r="C68" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>0.875</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>0.452</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the high bay warehouse waiting platform</t>
+          <t>moving towards the slot 5</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>191</v>
+        <v>71</v>
       </c>
       <c r="C69" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>0.429</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>transporting the bucket to the vacuum gripper robot crane jib</t>
+          <t>drilling the workpiece for 6 seconds</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>270</v>
+        <v>6</v>
       </c>
       <c r="C70" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="E70" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>0.282</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>0.786</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>0.415</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the sink 2</t>
+          <t>dropping off the workpiece at the high bay warehouse waiting platform</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E71" t="n">
         <v>2</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the high bay warehouse</t>
+          <t>ejecting the workpiece to the sink 1</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>173</v>
+        <v>4</v>
       </c>
       <c r="C72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D72" t="n">
         <v>4</v>
       </c>
       <c r="E72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the high bay warehouse waiting platform</t>
+          <t>ejecting the workpiece to the sink 3</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>0.200</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the sorting machine conveyor belt</t>
+          <t>picking up the workpiece from the sink 3</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C74" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E74" t="n">
         <v>0</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>0.300</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ejecting the workpiece to the sink 3</t>
+          <t>transporting the workpiece to the sink 3</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>29</v>
+        <v>77</v>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ejecting the workpiece to the conveyor belt</t>
+          <t>picking up the workpiece from the punching machine sink</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="C76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>0.100</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>moving towards the slot 7</t>
+          <t>picking up the workpiece from the sink 1</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ejecting the workpiece to the sink 1</t>
+          <t>picking up the workpiece from the sink 2</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
@@ -3079,20 +3079,20 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 28 seconds</t>
+          <t>transporting the bucket to the slot 7</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>12</v>
+        <v>143</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -3113,20 +3113,20 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>moving towards the punching machine sink</t>
+          <t>transporting the workpiece to the initial position</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>3</v>
+        <v>71</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -3147,11 +3147,11 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 15 seconds</t>
+          <t>dropping off the workpiece at the drilling machine sink</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
@@ -3160,7 +3160,7 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -3181,20 +3181,20 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 4 seconds</t>
+          <t>transporting the workpiece to the ejection position</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>2</v>
+        <v>110</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -3215,20 +3215,20 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ejecting the workpiece to the sink 2</t>
+          <t>moving towards the slot 1</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>27</v>
+        <v>163</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -3249,20 +3249,20 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 35 seconds</t>
+          <t>dropping off the workpiece at the sorting machine conveyor belt</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -3283,17 +3283,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the human workstation</t>
+          <t>moving towards the punching machine sink</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E85" t="n">
         <v>0</v>
@@ -3317,17 +3317,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>moving towards the sink 1</t>
+          <t>moving towards the slot 7</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="E86" t="n">
         <v>0</v>
@@ -3343,108 +3343,6 @@
         </is>
       </c>
       <c r="H86" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>drilling the workpiece for 20 seconds</t>
-        </is>
-      </c>
-      <c r="B87" t="n">
-        <v>30</v>
-      </c>
-      <c r="C87" t="n">
-        <v>0</v>
-      </c>
-      <c r="D87" t="n">
-        <v>0</v>
-      </c>
-      <c r="E87" t="n">
-        <v>1</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>dropping off the workpiece at the sorting machine conveyor belt</t>
-        </is>
-      </c>
-      <c r="B88" t="n">
-        <v>3</v>
-      </c>
-      <c r="C88" t="n">
-        <v>0</v>
-      </c>
-      <c r="D88" t="n">
-        <v>3</v>
-      </c>
-      <c r="E88" t="n">
-        <v>0</v>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>lowering the workpiece</t>
-        </is>
-      </c>
-      <c r="B89" t="n">
-        <v>38</v>
-      </c>
-      <c r="C89" t="n">
-        <v>0</v>
-      </c>
-      <c r="D89" t="n">
-        <v>0</v>
-      </c>
-      <c r="E89" t="n">
-        <v>2</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
         <is>
           <t>0.000</t>
         </is>

--- a/tables/autoencoder_per_event_metrics.xlsx
+++ b/tables/autoencoder_per_event_metrics.xlsx
@@ -495,11 +495,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 24 seconds</t>
+          <t>moving towards the slot 4</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
@@ -529,14 +529,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>milling the workpiece</t>
+          <t>drilling the workpiece for 20 seconds</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>106</v>
+        <v>30</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -563,14 +563,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>moving towards the slot 8</t>
+          <t>moving towards the slot 3</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>72</v>
+        <v>139</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -597,11 +597,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>moving towards the slot 4</t>
+          <t>lowering the workpiece</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
@@ -631,11 +631,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the oven</t>
+          <t>milling the workpiece</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
         <v>2</v>
@@ -665,7 +665,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 15 seconds</t>
+          <t>drilling the workpiece for 24 seconds</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -699,14 +699,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>moving towards the slot 3</t>
+          <t>drilling the workpiece for 15 seconds</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>139</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -733,14 +733,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>lowering the workpiece</t>
+          <t>dropping off the workpiece at the oven</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -767,11 +767,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 20 seconds</t>
+          <t>moving towards the slot 8</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="C11" t="n">
         <v>1</v>
@@ -1379,20 +1379,20 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the sink 2</t>
+          <t>picking up the bucket from the slot</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>70</v>
+        <v>1868</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1413,29 +1413,29 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>burning the workpiece for 30 seconds</t>
+          <t>transporting the workpiece to the high bay warehouse</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>256</v>
+        <v>173</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.571</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.800</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1447,29 +1447,29 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the high bay warehouse</t>
+          <t>transporting the workpiece to the sink 2</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>173</v>
+        <v>70</v>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1481,20 +1481,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the high bay warehouse waiting platform</t>
+          <t>burning the workpiece for 30 seconds</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>150</v>
+        <v>256</v>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1515,20 +1515,20 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>picking up the bucket from the slot</t>
+          <t>picking up the workpiece from the high bay warehouse waiting platform</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1868</v>
+        <v>150</v>
       </c>
       <c r="C33" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1855,11 +1855,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the dm_2_sink</t>
+          <t>transporting the bucket to the slot 6</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>97</v>
+        <v>193</v>
       </c>
       <c r="C43" t="n">
         <v>2</v>
@@ -1889,29 +1889,29 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the mill</t>
+          <t>transporting the bucket to the slot 5</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>217</v>
+        <v>101</v>
       </c>
       <c r="C44" t="n">
         <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.400</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -1923,11 +1923,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 6</t>
+          <t>transporting the workpiece to the dm_2_sink</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>193</v>
+        <v>97</v>
       </c>
       <c r="C45" t="n">
         <v>2</v>
@@ -1957,29 +1957,29 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 5</t>
+          <t>transporting the workpiece to the mill</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>101</v>
+        <v>217</v>
       </c>
       <c r="C46" t="n">
         <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2093,29 +2093,29 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>moving towards the slot 2</t>
+          <t>dropping off the workpiece at the high bay warehouse</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="C50" t="n">
         <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2127,11 +2127,11 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the high bay warehouse</t>
+          <t>ejecting the workpiece to the sink 2</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="C51" t="n">
         <v>1</v>
@@ -2161,29 +2161,29 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ejecting the workpiece to the sink 2</t>
+          <t>moving towards the slot 2</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>27</v>
+        <v>95</v>
       </c>
       <c r="C52" t="n">
         <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2331,29 +2331,29 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the light barrier 3</t>
+          <t>transporting the bucket to the slot 3</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>404</v>
+        <v>257</v>
       </c>
       <c r="C57" t="n">
         <v>3</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E57" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2365,29 +2365,29 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 3</t>
+          <t>transporting the workpiece to the light barrier 3</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>257</v>
+        <v>404</v>
       </c>
       <c r="C58" t="n">
         <v>3</v>
       </c>
       <c r="D58" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>0.273</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2671,20 +2671,20 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the sorting machine conveyor belt</t>
+          <t>picking up the workpiece from the sink 3</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -2705,20 +2705,20 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>moving towards the slot 6</t>
+          <t>transporting the workpiece to the sink 3</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="C68" t="n">
         <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -2739,20 +2739,20 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>moving towards the slot 5</t>
+          <t>transporting the workpiece to the sorting machine conveyor belt</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -2773,17 +2773,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 6 seconds</t>
+          <t>picking up the workpiece from the sink 2</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
@@ -2841,20 +2841,20 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ejecting the workpiece to the sink 1</t>
+          <t>dropping off the workpiece at the drilling machine sink</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -2875,17 +2875,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ejecting the workpiece to the sink 3</t>
+          <t>moving towards the slot 6</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>29</v>
+        <v>110</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
@@ -2909,17 +2909,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the sink 3</t>
+          <t>moving towards the slot 7</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E74" t="n">
         <v>0</v>
@@ -2943,20 +2943,20 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the sink 3</t>
+          <t>transporting the workpiece to the ejection position</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -2977,20 +2977,20 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the punching machine sink</t>
+          <t>drilling the workpiece for 6 seconds</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>83</v>
+        <v>6</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -3011,17 +3011,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the sink 1</t>
+          <t>moving towards the punching machine sink</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
@@ -3045,20 +3045,20 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the sink 2</t>
+          <t>moving towards the slot 1</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>60</v>
+        <v>163</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -3079,20 +3079,20 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 7</t>
+          <t>ejecting the workpiece to the sink 1</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>143</v>
+        <v>4</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -3113,20 +3113,20 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the initial position</t>
+          <t>picking up the workpiece from the sink 1</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>71</v>
+        <v>6</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -3147,11 +3147,11 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the drilling machine sink</t>
+          <t>picking up the workpiece from the punching machine sink</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
@@ -3160,7 +3160,7 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -3181,20 +3181,20 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the ejection position</t>
+          <t>ejecting the workpiece to the sink 3</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>110</v>
+        <v>29</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -3215,17 +3215,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>moving towards the slot 1</t>
+          <t>transporting the workpiece to the initial position</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>163</v>
+        <v>71</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E83" t="n">
         <v>2</v>
@@ -3249,17 +3249,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the sorting machine conveyor belt</t>
+          <t>moving towards the slot 5</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>3</v>
+        <v>71</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E84" t="n">
         <v>0</v>
@@ -3283,20 +3283,20 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>moving towards the punching machine sink</t>
+          <t>transporting the bucket to the slot 7</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>3</v>
+        <v>143</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -3317,11 +3317,11 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>moving towards the slot 7</t>
+          <t>dropping off the workpiece at the sorting machine conveyor belt</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>

--- a/tables/autoencoder_per_event_metrics.xlsx
+++ b/tables/autoencoder_per_event_metrics.xlsx
@@ -461,11 +461,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 35 seconds</t>
+          <t>drilling the workpiece for 24 seconds</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>moving towards the slot 4</t>
+          <t>dropping off the workpiece at the oven</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -529,11 +529,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 20 seconds</t>
+          <t>moving towards the slot 8</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
@@ -563,14 +563,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>moving towards the slot 3</t>
+          <t>moving towards the slot 4</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>139</v>
+        <v>65</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -665,11 +665,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 24 seconds</t>
+          <t>drilling the workpiece for 20 seconds</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
@@ -733,14 +733,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the oven</t>
+          <t>drilling the workpiece for 35 seconds</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -767,14 +767,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>moving towards the slot 8</t>
+          <t>moving towards the slot 3</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>72</v>
+        <v>139</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -1379,20 +1379,20 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>picking up the bucket from the slot</t>
+          <t>picking up the workpiece from the high bay warehouse waiting platform</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1868</v>
+        <v>150</v>
       </c>
       <c r="C29" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1413,29 +1413,29 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the high bay warehouse</t>
+          <t>transporting the workpiece to the sink 2</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>173</v>
+        <v>70</v>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1447,20 +1447,20 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the sink 2</t>
+          <t>picking up the bucket from the slot</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>70</v>
+        <v>1868</v>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1481,29 +1481,29 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>burning the workpiece for 30 seconds</t>
+          <t>transporting the workpiece to the high bay warehouse</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>256</v>
+        <v>173</v>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.571</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.800</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1515,20 +1515,20 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the high bay warehouse waiting platform</t>
+          <t>burning the workpiece for 30 seconds</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>150</v>
+        <v>256</v>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1821,29 +1821,29 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 8</t>
+          <t>transporting the bucket to the slot 6</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>100</v>
+        <v>193</v>
       </c>
       <c r="C42" t="n">
         <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -1855,29 +1855,29 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 6</t>
+          <t>transporting the bucket to the slot 5</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>193</v>
+        <v>101</v>
       </c>
       <c r="C43" t="n">
         <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.400</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -1889,29 +1889,29 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 5</t>
+          <t>transporting the workpiece to the dm_2_sink</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C44" t="n">
         <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -1923,11 +1923,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the dm_2_sink</t>
+          <t>transporting the workpiece to the mill</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>97</v>
+        <v>217</v>
       </c>
       <c r="C45" t="n">
         <v>2</v>
@@ -1957,29 +1957,29 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the mill</t>
+          <t>transporting the bucket to the slot 8</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>217</v>
+        <v>100</v>
       </c>
       <c r="C46" t="n">
         <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.400</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2127,29 +2127,29 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ejecting the workpiece to the sink 2</t>
+          <t>moving towards the slot 2</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>27</v>
+        <v>95</v>
       </c>
       <c r="C51" t="n">
         <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2161,11 +2161,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>moving towards the slot 2</t>
+          <t>dropping off the workpiece at the human workstation</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>95</v>
+        <v>53</v>
       </c>
       <c r="C52" t="n">
         <v>1</v>
@@ -2229,29 +2229,29 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the human workstation</t>
+          <t>ejecting the workpiece to the sink 2</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="C54" t="n">
         <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2331,29 +2331,29 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 3</t>
+          <t>transporting the bucket to the vacuum gripper robot crane jib</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="C57" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D57" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E57" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.286</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>0.857</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2399,29 +2399,29 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>transporting the bucket to the vacuum gripper robot crane jib</t>
+          <t>transporting the bucket to the slot 3</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="C59" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D59" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2501,11 +2501,11 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ejecting the workpiece to the conveyor belt</t>
+          <t>transporting the bucket to the high bay warehouse crane jib</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>113</v>
+        <v>159</v>
       </c>
       <c r="C62" t="n">
         <v>1</v>
@@ -2535,11 +2535,11 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>transporting the bucket to the high bay warehouse crane jib</t>
+          <t>ejecting the workpiece to the conveyor belt</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="C63" t="n">
         <v>1</v>
@@ -2671,20 +2671,20 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the sink 3</t>
+          <t>dropping off the workpiece at the drilling machine sink</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -2705,20 +2705,20 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the sink 3</t>
+          <t>picking up the workpiece from the sink 1</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C68" t="n">
         <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -2739,20 +2739,20 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the sorting machine conveyor belt</t>
+          <t>picking up the workpiece from the punching machine sink</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -2773,17 +2773,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the sink 2</t>
+          <t>moving towards the slot 7</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
@@ -2841,17 +2841,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the drilling machine sink</t>
+          <t>transporting the workpiece to the ejection position</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>53</v>
+        <v>110</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E72" t="n">
         <v>2</v>
@@ -2875,20 +2875,20 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>moving towards the slot 6</t>
+          <t>transporting the workpiece to the initial position</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -2909,17 +2909,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>moving towards the slot 7</t>
+          <t>picking up the workpiece from the sink 2</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E74" t="n">
         <v>0</v>
@@ -2943,11 +2943,11 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the ejection position</t>
+          <t>picking up the workpiece from the sink 3</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>110</v>
+        <v>46</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
@@ -2956,7 +2956,7 @@
         <v>1</v>
       </c>
       <c r="E75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -2977,17 +2977,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 6 seconds</t>
+          <t>dropping off the workpiece at the sorting machine conveyor belt</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
@@ -3011,17 +3011,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>moving towards the punching machine sink</t>
+          <t>moving towards the slot 6</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>3</v>
+        <v>110</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
@@ -3045,17 +3045,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>moving towards the slot 1</t>
+          <t>transporting the bucket to the slot 7</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E78" t="n">
         <v>2</v>
@@ -3079,17 +3079,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ejecting the workpiece to the sink 1</t>
+          <t>moving towards the slot 5</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>4</v>
+        <v>71</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
@@ -3113,11 +3113,11 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the sink 1</t>
+          <t>transporting the workpiece to the sorting machine conveyor belt</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
@@ -3126,7 +3126,7 @@
         <v>4</v>
       </c>
       <c r="E80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -3147,20 +3147,20 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the punching machine sink</t>
+          <t>moving towards the slot 1</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>83</v>
+        <v>163</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -3181,17 +3181,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ejecting the workpiece to the sink 3</t>
+          <t>moving towards the punching machine sink</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
@@ -3215,20 +3215,20 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the initial position</t>
+          <t>drilling the workpiece for 6 seconds</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>71</v>
+        <v>6</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -3249,11 +3249,11 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>moving towards the slot 5</t>
+          <t>ejecting the workpiece to the sink 3</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>71</v>
+        <v>29</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
@@ -3283,20 +3283,20 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 7</t>
+          <t>ejecting the workpiece to the sink 1</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>143</v>
+        <v>4</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -3317,20 +3317,20 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the sorting machine conveyor belt</t>
+          <t>transporting the workpiece to the sink 3</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>

--- a/tables/autoencoder_per_event_metrics.xlsx
+++ b/tables/autoencoder_per_event_metrics.xlsx
@@ -461,7 +461,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 24 seconds</t>
+          <t>drilling the workpiece for 15 seconds</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the oven</t>
+          <t>drilling the workpiece for 20 seconds</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>82</v>
+        <v>30</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -597,11 +597,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>lowering the workpiece</t>
+          <t>drilling the workpiece for 24 seconds</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
@@ -631,14 +631,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>milling the workpiece</t>
+          <t>moving towards the slot 3</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -665,11 +665,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 20 seconds</t>
+          <t>lowering the workpiece</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
@@ -699,11 +699,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 15 seconds</t>
+          <t>drilling the workpiece for 35 seconds</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
@@ -733,14 +733,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 35 seconds</t>
+          <t>milling the workpiece</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -767,14 +767,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>moving towards the slot 3</t>
+          <t>dropping off the workpiece at the oven</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -1379,20 +1379,20 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the high bay warehouse waiting platform</t>
+          <t>picking up the bucket from the slot</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>150</v>
+        <v>1868</v>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1413,11 +1413,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the sink 2</t>
+          <t>burning the workpiece for 30 seconds</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>70</v>
+        <v>256</v>
       </c>
       <c r="C30" t="n">
         <v>1</v>
@@ -1447,20 +1447,20 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>picking up the bucket from the slot</t>
+          <t>picking up the workpiece from the high bay warehouse waiting platform</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1868</v>
+        <v>150</v>
       </c>
       <c r="C31" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1481,29 +1481,29 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the high bay warehouse</t>
+          <t>transporting the workpiece to the sink 2</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>173</v>
+        <v>70</v>
       </c>
       <c r="C32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1515,29 +1515,29 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>burning the workpiece for 30 seconds</t>
+          <t>transporting the workpiece to the high bay warehouse</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>256</v>
+        <v>173</v>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E33" t="n">
         <v>1</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.571</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.800</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1821,29 +1821,29 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 6</t>
+          <t>transporting the bucket to the slot 8</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>193</v>
+        <v>100</v>
       </c>
       <c r="C42" t="n">
         <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.400</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -1855,29 +1855,29 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 5</t>
+          <t>transporting the bucket to the slot 6</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>101</v>
+        <v>193</v>
       </c>
       <c r="C43" t="n">
         <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -1889,11 +1889,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the dm_2_sink</t>
+          <t>transporting the workpiece to the mill</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>97</v>
+        <v>217</v>
       </c>
       <c r="C44" t="n">
         <v>2</v>
@@ -1923,11 +1923,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the mill</t>
+          <t>transporting the workpiece to the dm_2_sink</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>217</v>
+        <v>97</v>
       </c>
       <c r="C45" t="n">
         <v>2</v>
@@ -1957,11 +1957,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 8</t>
+          <t>transporting the bucket to the slot 5</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C46" t="n">
         <v>2</v>
@@ -2093,11 +2093,11 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the high bay warehouse</t>
+          <t>ejecting the workpiece to the sink 2</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="C50" t="n">
         <v>1</v>
@@ -2127,20 +2127,20 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>moving towards the slot 2</t>
+          <t>picking up the workpiece from the drilling machine sink</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>95</v>
+        <v>296</v>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -2195,29 +2195,29 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the drilling machine sink</t>
+          <t>dropping off the workpiece at the high bay warehouse</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>296</v>
+        <v>38</v>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2229,29 +2229,29 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ejecting the workpiece to the sink 2</t>
+          <t>moving towards the slot 2</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>27</v>
+        <v>95</v>
       </c>
       <c r="C54" t="n">
         <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2671,20 +2671,20 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the drilling machine sink</t>
+          <t>ejecting the workpiece to the sink 3</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -2705,11 +2705,11 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the sink 1</t>
+          <t>ejecting the workpiece to the sink 1</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C68" t="n">
         <v>0</v>
@@ -2739,11 +2739,11 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the punching machine sink</t>
+          <t>transporting the workpiece to the initial position</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
@@ -2752,7 +2752,7 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -2773,17 +2773,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>moving towards the slot 7</t>
+          <t>moving towards the slot 5</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
@@ -2807,20 +2807,20 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the high bay warehouse waiting platform</t>
+          <t>drilling the workpiece for 6 seconds</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -2841,20 +2841,20 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the ejection position</t>
+          <t>moving towards the punching machine sink</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>110</v>
+        <v>3</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -2875,17 +2875,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the initial position</t>
+          <t>transporting the bucket to the slot 7</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E73" t="n">
         <v>2</v>
@@ -2909,17 +2909,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the sink 2</t>
+          <t>picking up the workpiece from the sink 3</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E74" t="n">
         <v>0</v>
@@ -2943,20 +2943,20 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the sink 3</t>
+          <t>transporting the workpiece to the sink 3</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -2977,20 +2977,20 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the sorting machine conveyor belt</t>
+          <t>transporting the workpiece to the sorting machine conveyor belt</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>moving towards the slot 6</t>
+          <t>transporting the workpiece to the ejection position</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3024,7 +3024,7 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -3045,20 +3045,20 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 7</t>
+          <t>moving towards the slot 6</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>143</v>
+        <v>110</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -3079,17 +3079,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>moving towards the slot 5</t>
+          <t>moving towards the slot 7</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
@@ -3113,17 +3113,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the sorting machine conveyor belt</t>
+          <t>moving towards the slot 1</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>50</v>
+        <v>163</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E80" t="n">
         <v>2</v>
@@ -3147,17 +3147,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>moving towards the slot 1</t>
+          <t>dropping off the workpiece at the high bay warehouse waiting platform</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>163</v>
+        <v>46</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E81" t="n">
         <v>2</v>
@@ -3181,7 +3181,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>moving towards the punching machine sink</t>
+          <t>dropping off the workpiece at the sorting machine conveyor belt</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -3215,20 +3215,20 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 6 seconds</t>
+          <t>dropping off the workpiece at the drilling machine sink</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -3249,17 +3249,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ejecting the workpiece to the sink 3</t>
+          <t>picking up the workpiece from the sink 1</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E84" t="n">
         <v>0</v>
@@ -3283,17 +3283,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ejecting the workpiece to the sink 1</t>
+          <t>picking up the workpiece from the sink 2</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E85" t="n">
         <v>0</v>
@@ -3317,11 +3317,11 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the sink 3</t>
+          <t>picking up the workpiece from the punching machine sink</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>

--- a/tables/autoencoder_per_event_metrics.xlsx
+++ b/tables/autoencoder_per_event_metrics.xlsx
@@ -461,14 +461,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 15 seconds</t>
+          <t>moving towards the slot 3</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26</v>
+        <v>139</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 20 seconds</t>
+          <t>dropping off the workpiece at the oven</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -529,11 +529,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>moving towards the slot 8</t>
+          <t>drilling the workpiece for 20 seconds</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
@@ -563,14 +563,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>moving towards the slot 4</t>
+          <t>milling the workpiece</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65</v>
+        <v>106</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -597,11 +597,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 24 seconds</t>
+          <t>moving towards the slot 8</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
@@ -631,14 +631,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>moving towards the slot 3</t>
+          <t>moving towards the slot 4</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>139</v>
+        <v>65</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -665,11 +665,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lowering the workpiece</t>
+          <t>drilling the workpiece for 15 seconds</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
@@ -733,14 +733,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>milling the workpiece</t>
+          <t>lowering the workpiece</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>106</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -767,14 +767,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the oven</t>
+          <t>drilling the workpiece for 24 seconds</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>82</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -1413,29 +1413,29 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>burning the workpiece for 30 seconds</t>
+          <t>transporting the workpiece to the high bay warehouse</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>256</v>
+        <v>173</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.571</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.800</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1447,20 +1447,20 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the high bay warehouse waiting platform</t>
+          <t>burning the workpiece for 30 seconds</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>150</v>
+        <v>256</v>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1515,29 +1515,29 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the high bay warehouse</t>
+          <t>picking up the workpiece from the high bay warehouse waiting platform</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1821,29 +1821,29 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 8</t>
+          <t>transporting the bucket to the slot 6</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>100</v>
+        <v>193</v>
       </c>
       <c r="C42" t="n">
         <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -1855,29 +1855,29 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 6</t>
+          <t>transporting the bucket to the slot 5</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>193</v>
+        <v>101</v>
       </c>
       <c r="C43" t="n">
         <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.400</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -1957,11 +1957,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 5</t>
+          <t>transporting the bucket to the slot 8</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C46" t="n">
         <v>2</v>
@@ -2093,29 +2093,29 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ejecting the workpiece to the sink 2</t>
+          <t>dropping off the workpiece at the human workstation</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="C50" t="n">
         <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2161,29 +2161,29 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the human workstation</t>
+          <t>ejecting the workpiece to the sink 2</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="C52" t="n">
         <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2331,29 +2331,29 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>transporting the bucket to the vacuum gripper robot crane jib</t>
+          <t>transporting the bucket to the slot 3</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="C57" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D57" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2399,29 +2399,29 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 3</t>
+          <t>transporting the bucket to the vacuum gripper robot crane jib</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="C59" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D59" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E59" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.286</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>0.857</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2501,11 +2501,11 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>transporting the bucket to the high bay warehouse crane jib</t>
+          <t>ejecting the workpiece to the conveyor belt</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="C62" t="n">
         <v>1</v>
@@ -2535,11 +2535,11 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ejecting the workpiece to the conveyor belt</t>
+          <t>transporting the bucket to the high bay warehouse crane jib</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>113</v>
+        <v>159</v>
       </c>
       <c r="C63" t="n">
         <v>1</v>
@@ -2671,20 +2671,20 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ejecting the workpiece to the sink 3</t>
+          <t>dropping off the workpiece at the high bay warehouse waiting platform</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -2739,20 +2739,20 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the initial position</t>
+          <t>drilling the workpiece for 6 seconds</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>71</v>
+        <v>6</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -2773,17 +2773,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>moving towards the slot 5</t>
+          <t>dropping off the workpiece at the sorting machine conveyor belt</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>71</v>
+        <v>3</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
@@ -2807,20 +2807,20 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 6 seconds</t>
+          <t>dropping off the workpiece at the drilling machine sink</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -2841,17 +2841,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>moving towards the punching machine sink</t>
+          <t>moving towards the slot 5</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>3</v>
+        <v>71</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E72" t="n">
         <v>0</v>
@@ -2875,20 +2875,20 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 7</t>
+          <t>picking up the workpiece from the punching machine sink</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -2909,11 +2909,11 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the sink 3</t>
+          <t>moving towards the slot 6</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>46</v>
+        <v>110</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
@@ -3045,20 +3045,20 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>moving towards the slot 6</t>
+          <t>moving towards the slot 1</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>110</v>
+        <v>163</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -3079,17 +3079,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>moving towards the slot 7</t>
+          <t>picking up the workpiece from the sink 1</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
@@ -3113,17 +3113,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>moving towards the slot 1</t>
+          <t>transporting the workpiece to the initial position</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>163</v>
+        <v>71</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E80" t="n">
         <v>2</v>
@@ -3147,20 +3147,20 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the high bay warehouse waiting platform</t>
+          <t>picking up the workpiece from the sink 2</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the sorting machine conveyor belt</t>
+          <t>moving towards the punching machine sink</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -3215,20 +3215,20 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the drilling machine sink</t>
+          <t>moving towards the slot 7</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -3249,20 +3249,20 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the sink 1</t>
+          <t>transporting the bucket to the slot 7</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>6</v>
+        <v>143</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -3283,11 +3283,11 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the sink 2</t>
+          <t>ejecting the workpiece to the sink 3</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
@@ -3317,20 +3317,20 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the punching machine sink</t>
+          <t>picking up the workpiece from the sink 3</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>

--- a/tables/autoencoder_per_event_metrics.xlsx
+++ b/tables/autoencoder_per_event_metrics.xlsx
@@ -461,14 +461,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>moving towards the slot 3</t>
+          <t>moving towards the slot 4</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>139</v>
+        <v>65</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the oven</t>
+          <t>drilling the workpiece for 15 seconds</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>82</v>
+        <v>26</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -529,14 +529,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 20 seconds</t>
+          <t>milling the workpiece</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30</v>
+        <v>106</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -563,14 +563,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>milling the workpiece</t>
+          <t>drilling the workpiece for 35 seconds</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>106</v>
+        <v>22</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -597,11 +597,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>moving towards the slot 8</t>
+          <t>drilling the workpiece for 24 seconds</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
@@ -631,14 +631,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>moving towards the slot 4</t>
+          <t>dropping off the workpiece at the oven</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -665,14 +665,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 15 seconds</t>
+          <t>moving towards the slot 3</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26</v>
+        <v>139</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -699,11 +699,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 35 seconds</t>
+          <t>lowering the workpiece</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
@@ -733,11 +733,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>lowering the workpiece</t>
+          <t>moving towards the slot 8</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
@@ -767,11 +767,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 24 seconds</t>
+          <t>drilling the workpiece for 20 seconds</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
         <v>1</v>
@@ -1379,20 +1379,20 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>picking up the bucket from the slot</t>
+          <t>burning the workpiece for 30 seconds</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1868</v>
+        <v>256</v>
       </c>
       <c r="C29" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1447,20 +1447,20 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>burning the workpiece for 30 seconds</t>
+          <t>picking up the bucket from the slot</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>256</v>
+        <v>1868</v>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1821,29 +1821,29 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 6</t>
+          <t>transporting the bucket to the slot 8</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>193</v>
+        <v>100</v>
       </c>
       <c r="C42" t="n">
         <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.400</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -1855,29 +1855,29 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 5</t>
+          <t>transporting the bucket to the slot 6</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>101</v>
+        <v>193</v>
       </c>
       <c r="C43" t="n">
         <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -1889,29 +1889,29 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the mill</t>
+          <t>transporting the bucket to the slot 5</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>217</v>
+        <v>101</v>
       </c>
       <c r="C44" t="n">
         <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.400</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -1923,11 +1923,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the dm_2_sink</t>
+          <t>transporting the workpiece to the mill</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>97</v>
+        <v>217</v>
       </c>
       <c r="C45" t="n">
         <v>2</v>
@@ -1957,29 +1957,29 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 8</t>
+          <t>transporting the workpiece to the dm_2_sink</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C46" t="n">
         <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2093,11 +2093,11 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the human workstation</t>
+          <t>moving towards the slot 2</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="C50" t="n">
         <v>1</v>
@@ -2127,29 +2127,29 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the drilling machine sink</t>
+          <t>ejecting the workpiece to the sink 2</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>296</v>
+        <v>27</v>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2161,29 +2161,29 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ejecting the workpiece to the sink 2</t>
+          <t>dropping off the workpiece at the human workstation</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="C52" t="n">
         <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2229,20 +2229,20 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>moving towards the slot 2</t>
+          <t>picking up the workpiece from the drilling machine sink</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>95</v>
+        <v>296</v>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D54" t="n">
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -2331,29 +2331,29 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 3</t>
+          <t>transporting the workpiece to the light barrier 3</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>257</v>
+        <v>404</v>
       </c>
       <c r="C57" t="n">
         <v>3</v>
       </c>
       <c r="D57" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>0.273</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2365,29 +2365,29 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the light barrier 3</t>
+          <t>transporting the bucket to the slot 3</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>404</v>
+        <v>257</v>
       </c>
       <c r="C58" t="n">
         <v>3</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2501,11 +2501,11 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ejecting the workpiece to the conveyor belt</t>
+          <t>transporting the bucket to the high bay warehouse crane jib</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>113</v>
+        <v>159</v>
       </c>
       <c r="C62" t="n">
         <v>1</v>
@@ -2535,11 +2535,11 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>transporting the bucket to the high bay warehouse crane jib</t>
+          <t>ejecting the workpiece to the conveyor belt</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="C63" t="n">
         <v>1</v>
@@ -2671,11 +2671,11 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the high bay warehouse waiting platform</t>
+          <t>moving towards the slot 7</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
@@ -2684,7 +2684,7 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -2705,17 +2705,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ejecting the workpiece to the sink 1</t>
+          <t>ejecting the workpiece to the sink 3</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="C68" t="n">
         <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E68" t="n">
         <v>0</v>
@@ -2739,17 +2739,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 6 seconds</t>
+          <t>moving towards the slot 6</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>6</v>
+        <v>110</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E69" t="n">
         <v>0</v>
@@ -2773,17 +2773,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the sorting machine conveyor belt</t>
+          <t>picking up the workpiece from the sink 3</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
@@ -2807,17 +2807,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the drilling machine sink</t>
+          <t>dropping off the workpiece at the high bay warehouse waiting platform</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E71" t="n">
         <v>2</v>
@@ -2841,11 +2841,11 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>moving towards the slot 5</t>
+          <t>transporting the bucket to the slot 7</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
@@ -2854,7 +2854,7 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -2875,20 +2875,20 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the punching machine sink</t>
+          <t>moving towards the slot 1</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>83</v>
+        <v>163</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -2909,20 +2909,20 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>moving towards the slot 6</t>
+          <t>transporting the workpiece to the sink 3</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -2943,11 +2943,11 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the sink 3</t>
+          <t>picking up the workpiece from the punching machine sink</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
@@ -2977,17 +2977,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the sorting machine conveyor belt</t>
+          <t>dropping off the workpiece at the drilling machine sink</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
         <v>2</v>
@@ -3011,20 +3011,20 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the ejection position</t>
+          <t>moving towards the slot 5</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -3045,17 +3045,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>moving towards the slot 1</t>
+          <t>transporting the workpiece to the sorting machine conveyor belt</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>163</v>
+        <v>50</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E78" t="n">
         <v>2</v>
@@ -3079,11 +3079,11 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the sink 1</t>
+          <t>ejecting the workpiece to the sink 1</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
@@ -3113,20 +3113,20 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the initial position</t>
+          <t>moving towards the punching machine sink</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>71</v>
+        <v>3</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -3147,20 +3147,20 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the sink 2</t>
+          <t>transporting the workpiece to the initial position</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -3181,17 +3181,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>moving towards the punching machine sink</t>
+          <t>picking up the workpiece from the sink 1</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
@@ -3215,17 +3215,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>moving towards the slot 7</t>
+          <t>drilling the workpiece for 6 seconds</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
@@ -3249,17 +3249,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 7</t>
+          <t>transporting the workpiece to the ejection position</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>143</v>
+        <v>110</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E84" t="n">
         <v>2</v>
@@ -3283,17 +3283,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ejecting the workpiece to the sink 3</t>
+          <t>dropping off the workpiece at the sorting machine conveyor belt</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E85" t="n">
         <v>0</v>
@@ -3317,17 +3317,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the sink 3</t>
+          <t>picking up the workpiece from the sink 2</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E86" t="n">
         <v>0</v>

--- a/tables/autoencoder_per_event_metrics.xlsx
+++ b/tables/autoencoder_per_event_metrics.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H86"/>
+  <dimension ref="A1:H89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,11 +461,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>moving towards the slot 4</t>
+          <t>dropping off the workpiece at the high bay warehouse</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -495,11 +495,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 15 seconds</t>
+          <t>picking up the workpiece from the human workstation</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26</v>
+        <v>194</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
@@ -529,14 +529,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>milling the workpiece</t>
+          <t>burning the workpiece for 30 seconds</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>106</v>
+        <v>256</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -563,14 +563,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 35 seconds</t>
+          <t>dropping off the workpiece at the human workstation</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -597,14 +597,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 24 seconds</t>
+          <t>drilling the workpiece for 35 seconds</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -631,11 +631,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the oven</t>
+          <t>drilling the workpiece for 20 seconds</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>82</v>
+        <v>30</v>
       </c>
       <c r="C7" t="n">
         <v>2</v>
@@ -665,11 +665,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>moving towards the slot 3</t>
+          <t>dropping off the workpiece at the oven</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="C8" t="n">
         <v>3</v>
@@ -699,11 +699,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>lowering the workpiece</t>
+          <t>drilling the workpiece for 21 seconds</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
@@ -733,20 +733,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>moving towards the slot 8</t>
+          <t>opening the oven door</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>72</v>
+        <v>867</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -755,32 +755,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.938</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.968</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 20 seconds</t>
+          <t>burning the workpiece for 25 seconds</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>516</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -789,60 +789,60 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.917</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.957</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>burning the workpiece for 25 seconds</t>
+          <t>transporting the bucket to the slot 6</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>516</v>
+        <v>193</v>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.833</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.889</t>
+          <t>0.909</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>moving towards the sink 2</t>
+          <t>picking up the workpiece from the high bay warehouse</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>244</v>
+        <v>360</v>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -857,202 +857,202 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.778</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>0.875</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>burning the workpiece for 20 seconds</t>
+          <t>burning the workpiece for 15 seconds</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>534</v>
+        <v>451</v>
       </c>
       <c r="C14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.765</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.929</t>
+          <t>0.769</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.839</t>
+          <t>0.870</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the milling_machine</t>
+          <t>burning the workpiece for 20 seconds</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2518</v>
+        <v>534</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="D15" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.805</t>
+          <t>0.765</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.805</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.805</t>
+          <t>0.867</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the pm_1_sink</t>
+          <t>moving towards the sink 2</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>91</v>
+        <v>244</v>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>0.857</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>temper the workpiece for 40 seconds</t>
+          <t>transporting the workpiece to the sink 3</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1346</v>
+        <v>77</v>
       </c>
       <c r="C17" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.821</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.719</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.767</t>
+          <t>0.857</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the punch or drill</t>
+          <t>temper the workpiece for 40 seconds</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>746</v>
+        <v>1346</v>
       </c>
       <c r="C18" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.861</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.619</t>
+          <t>0.756</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.765</t>
+          <t>0.805</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>burning the workpiece for 15 seconds</t>
+          <t>milling the workpiece</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>451</v>
+        <v>106</v>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1061,66 +1061,66 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.615</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.762</t>
+          <t>0.800</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 4</t>
+          <t>transporting the workpiece to the sink 2</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>158</v>
+        <v>70</v>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>0.667</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>0.857</t>
-        </is>
-      </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.800</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>opening the oven door</t>
+          <t>picking up the workpiece from the drilling machine sink</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>867</v>
+        <v>296</v>
       </c>
       <c r="C21" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1129,138 +1129,138 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.579</t>
+          <t>0.625</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.733</t>
+          <t>0.769</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>UNKNOWN_EVENT</t>
+          <t>transporting the workpiece to the light barrier 3</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>8244</v>
+        <v>404</v>
       </c>
       <c r="C22" t="n">
-        <v>138</v>
+        <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.798</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.670</t>
+          <t>0.625</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.728</t>
+          <t>0.769</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>dropping off the bucket at the slot</t>
+          <t>picking up the workpiece from the oven</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2069</v>
+        <v>1202</v>
       </c>
       <c r="C23" t="n">
         <v>27</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E23" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.794</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>0.730</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.711</t>
+          <t>0.761</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the drilling machine sink</t>
+          <t>transporting the workpiece to the milling_machine</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1297</v>
+        <v>2518</v>
       </c>
       <c r="C24" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E24" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.737</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.548</t>
+          <t>0.778</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.708</t>
+          <t>0.757</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the inside of the oven</t>
+          <t>ejecting the workpiece to the sink 2</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>474</v>
+        <v>27</v>
       </c>
       <c r="C25" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1270,129 +1270,129 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.706</t>
+          <t>0.750</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 1</t>
+          <t>transporting the bucket to the conveyor belt</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>326</v>
+        <v>2376</v>
       </c>
       <c r="C26" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="D26" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>0.917</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>0.635</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.706</t>
+          <t>0.750</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>moving towards the oven</t>
+          <t>transporting the bucket to the slot 7</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2451</v>
+        <v>143</v>
       </c>
       <c r="C27" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="D27" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.755</t>
+          <t>0.600</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.649</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.698</t>
+          <t>0.750</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>transporting the bucket to the high-bay warehouse crane jib</t>
+          <t>transporting the workpiece to the oven</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>907</v>
+        <v>1627</v>
       </c>
       <c r="C28" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.867</t>
+          <t>0.966</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.565</t>
+          <t>0.596</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.684</t>
+          <t>0.737</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>burning the workpiece for 30 seconds</t>
+          <t>transporting the workpiece to the drilling machine sink</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>256</v>
+        <v>1297</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1401,66 +1401,66 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.581</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.735</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the high bay warehouse</t>
+          <t>picking up the bucket from the slot</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>173</v>
+        <v>1868</v>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>0.574</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.729</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>picking up the bucket from the slot</t>
+          <t>moving towards the slot 3</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1868</v>
+        <v>139</v>
       </c>
       <c r="C31" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1469,32 +1469,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.571</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.727</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the sink 2</t>
+          <t>transporting the workpiece to the punch or drill</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>70</v>
+        <v>746</v>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1503,168 +1503,168 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.562</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.720</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the high bay warehouse waiting platform</t>
+          <t>UNKNOWN_EVENT</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>150</v>
+        <v>8244</v>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.790</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.653</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.715</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the oven</t>
+          <t>dropping off the bucket at the slot</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1627</v>
+        <v>2069</v>
       </c>
       <c r="C34" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
         <v>21</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.952</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.488</t>
+          <t>0.533</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.645</t>
+          <t>0.696</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the oven</t>
+          <t>transporting the bucket to the high-bay warehouse crane jib</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1202</v>
+        <v>907</v>
       </c>
       <c r="C35" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D35" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.650</t>
+          <t>0.875</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.619</t>
+          <t>0.560</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.634</t>
+          <t>0.683</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>picking up the bucket from the conveyor belt</t>
+          <t>moving towards the oven</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1832</v>
+        <v>2451</v>
       </c>
       <c r="C36" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="D36" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E36" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.840</t>
+          <t>0.765</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.600</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.627</t>
+          <t>0.672</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the high bay warehouse</t>
+          <t>moving towards the slot 2</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>360</v>
+        <v>95</v>
       </c>
       <c r="C37" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1673,196 +1673,196 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.455</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.625</t>
+          <t>0.667</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the human workstation</t>
+          <t>transporting the workpiece to the initial position</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>924</v>
+        <v>71</v>
       </c>
       <c r="C38" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.765</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0.520</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.619</t>
+          <t>0.667</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>transporting the bucket to the conveyor belt</t>
+          <t>picking up the workpiece from the high bay warehouse waiting platform</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2376</v>
+        <v>150</v>
       </c>
       <c r="C39" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.900</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.458</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.607</t>
+          <t>0.667</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>calibrating motor 3</t>
+          <t>transporting the bucket to the slot 3</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>5003</v>
+        <v>257</v>
       </c>
       <c r="C40" t="n">
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="D40" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0.808</t>
+          <t>0.625</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.480</t>
+          <t>0.714</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0.602</t>
+          <t>0.667</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the sorting machine</t>
+          <t>transporting the bucket to the slot 4</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1029</v>
+        <v>158</v>
       </c>
       <c r="C41" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E41" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.406</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.578</t>
+          <t>0.667</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 8</t>
+          <t>moving towards the slot 8</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>0.667</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 6</t>
+          <t>moving towards the slot 6</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>193</v>
+        <v>110</v>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D43" t="n">
         <v>1</v>
@@ -1872,187 +1872,187 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
+          <t>0.750</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>0.600</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
           <t>0.667</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>0.500</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>0.571</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 5</t>
+          <t>calibrating motor 2</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>101</v>
+        <v>2036</v>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="D44" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.774</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.545</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>0.640</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the mill</t>
+          <t>transporting the bucket to the slot 0</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>217</v>
+        <v>652</v>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E45" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.615</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.615</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>0.615</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the dm_2_sink</t>
+          <t>picking up the bucket from the conveyor belt</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>97</v>
+        <v>1832</v>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E46" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.867</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.441</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>0.584</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 0</t>
+          <t>transporting the bucket to the slot 1</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>652</v>
+        <v>326</v>
       </c>
       <c r="C47" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D47" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E47" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>0.438</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>0.875</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>0.583</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>moving towards the slot 0</t>
+          <t>transporting the workpiece to the drill</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>551</v>
+        <v>242</v>
       </c>
       <c r="C48" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>0.889</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>0.381</t>
+          <t>0.400</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>0.533</t>
+          <t>0.571</t>
         </is>
       </c>
     </row>
@@ -2066,81 +2066,81 @@
         <v>522</v>
       </c>
       <c r="C49" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D49" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E49" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0.429</t>
+          <t>0.423</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.846</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0.522</t>
+          <t>0.564</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>moving towards the slot 2</t>
+          <t>calibrating motor 3</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>95</v>
+        <v>5003</v>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E50" t="n">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.797</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.414</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.545</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ejecting the workpiece to the sink 2</t>
+          <t>transporting the workpiece to the inside of the oven</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>27</v>
+        <v>474</v>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -2149,41 +2149,41 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.545</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.522</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the human workstation</t>
+          <t>picking up the workpiece from the sink 3</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C52" t="n">
         <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2195,29 +2195,29 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the high bay warehouse</t>
+          <t>transporting the bucket to the slot 2</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>38</v>
+        <v>124</v>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E53" t="n">
         <v>1</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.400</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2229,29 +2229,29 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the drilling machine sink</t>
+          <t>transporting the workpiece to the human workstation</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>296</v>
+        <v>924</v>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E54" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.400</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2263,527 +2263,527 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>calibrating motor 2</t>
+          <t>transporting the workpiece to the pm_1_sink</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2036</v>
+        <v>91</v>
       </c>
       <c r="C55" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D55" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E55" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>0.720</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>0.327</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>0.450</t>
+          <t>0.500</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 2</t>
+          <t>drilling the workpiece for 9 seconds</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>124</v>
+        <v>18</v>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
         <v>2</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
           <t>0.500</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>0.444</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the light barrier 3</t>
+          <t>moving towards the slot 0</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>404</v>
+        <v>551</v>
       </c>
       <c r="C57" t="n">
         <v>3</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>0.429</t>
+          <t>0.500</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 3</t>
+          <t>transporting the bucket to the high bay warehouse crane jib</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>257</v>
+        <v>159</v>
       </c>
       <c r="C58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D58" t="n">
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
+          <t>0.400</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
           <t>0.500</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>0.375</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>0.429</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>transporting the bucket to the vacuum gripper robot crane jib</t>
+          <t>transporting the workpiece to the sorting machine</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>270</v>
+        <v>1029</v>
       </c>
       <c r="C59" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D59" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>0.321</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>0.429</t>
+          <t>0.486</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the punch</t>
+          <t>transporting the bucket to the vacuum gripper robot crane jib</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>350</v>
+        <v>270</v>
       </c>
       <c r="C60" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D60" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E60" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>0.364</t>
+          <t>0.700</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>0.421</t>
+          <t>0.452</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the high bay warehouse waiting platform</t>
+          <t>transporting the workpiece to the mill</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>191</v>
+        <v>217</v>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.444</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>transporting the bucket to the high bay warehouse crane jib</t>
+          <t>moving towards the sink 3</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>159</v>
+        <v>190</v>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D62" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E62" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.357</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.556</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>0.435</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ejecting the workpiece to the conveyor belt</t>
+          <t>transporting the workpiece to the high bay warehouse</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>113</v>
+        <v>173</v>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D63" t="n">
         <v>3</v>
       </c>
       <c r="E63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.400</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.400</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>0.400</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the drill</t>
+          <t>transporting the workpiece to the ejection position</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>242</v>
+        <v>110</v>
       </c>
       <c r="C64" t="n">
         <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>0.400</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>moving towards the sink 3</t>
+          <t>moving towards the slot 1</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>190</v>
+        <v>163</v>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D65" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E65" t="n">
         <v>4</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>0.100</t>
+          <t>0.300</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>0.200</t>
+          <t>0.429</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.353</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>moving towards the sink 1</t>
+          <t>transporting the workpiece to the high bay warehouse waiting platform</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="C66" t="n">
         <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>0.250</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0.333</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>moving towards the slot 7</t>
+          <t>transporting the bucket to the slot 5</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>50</v>
+        <v>101</v>
       </c>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D67" t="n">
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.250</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.333</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ejecting the workpiece to the sink 3</t>
+          <t>transporting the workpiece to the punch</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>29</v>
+        <v>350</v>
       </c>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D68" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.182</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.235</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>moving towards the slot 6</t>
+          <t>moving towards the sink 1</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>110</v>
+        <v>31</v>
       </c>
       <c r="C69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D69" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E69" t="n">
         <v>0</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.160</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the sink 3</t>
+          <t>transporting the bucket to the slot 8</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
@@ -2807,20 +2807,20 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the high bay warehouse waiting platform</t>
+          <t>dropping off the workpiece at the drilling machine sink</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -2841,20 +2841,20 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 7</t>
+          <t>ejecting the workpiece to the conveyor belt</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -2875,20 +2875,20 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>moving towards the slot 1</t>
+          <t>drilling the workpiece for 6 seconds</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>163</v>
+        <v>6</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -2909,11 +2909,11 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the sink 3</t>
+          <t>drilling the workpiece for 24 seconds</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>77</v>
+        <v>26</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
@@ -2943,20 +2943,20 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the punching machine sink</t>
+          <t>transporting the workpiece to the sorting machine conveyor belt</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -2977,20 +2977,20 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the drilling machine sink</t>
+          <t>dropping off the workpiece at the sorting machine conveyor belt</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -3011,20 +3011,20 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>moving towards the slot 5</t>
+          <t>moving towards the slot 4</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -3045,20 +3045,20 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the sorting machine conveyor belt</t>
+          <t>ejecting the workpiece to the sink 3</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -3079,20 +3079,20 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ejecting the workpiece to the sink 1</t>
+          <t>picking up the workpiece from the punching machine sink</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>4</v>
+        <v>83</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -3113,20 +3113,20 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>moving towards the punching machine sink</t>
+          <t>picking up the workpiece from the sink 2</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -3147,11 +3147,11 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the initial position</t>
+          <t>drilling the workpiece for 30 seconds</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>71</v>
+        <v>12</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
@@ -3160,7 +3160,7 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -3181,11 +3181,11 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the sink 1</t>
+          <t>ejecting the workpiece to the sink 1</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
@@ -3215,20 +3215,20 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 6 seconds</t>
+          <t>dropping off the workpiece at the high bay warehouse waiting platform</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -3249,20 +3249,20 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the ejection position</t>
+          <t>transporting the workpiece to the dm_2_sink</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -3283,20 +3283,20 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the sorting machine conveyor belt</t>
+          <t>drilling the workpiece for 3 seconds</t>
         </is>
       </c>
       <c r="B85" t="n">
+        <v>43</v>
+      </c>
+      <c r="C85" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" t="n">
         <v>3</v>
-      </c>
-      <c r="C85" t="n">
-        <v>0</v>
-      </c>
-      <c r="D85" t="n">
-        <v>3</v>
-      </c>
-      <c r="E85" t="n">
-        <v>0</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -3317,11 +3317,11 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the sink 2</t>
+          <t>moving towards the slot 5</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
@@ -3330,7 +3330,7 @@
         <v>2</v>
       </c>
       <c r="E86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -3343,6 +3343,108 @@
         </is>
       </c>
       <c r="H86" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>moving towards the slot 7</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>50</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" t="n">
+        <v>3</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>picking up the workpiece from the sink 1</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>6</v>
+      </c>
+      <c r="C88" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" t="n">
+        <v>4</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>moving towards the punching machine sink</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>3</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" t="n">
+        <v>3</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
         <is>
           <t>0.000</t>
         </is>

--- a/tables/autoencoder_per_event_metrics.xlsx
+++ b/tables/autoencoder_per_event_metrics.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H89"/>
+  <dimension ref="A1:H86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,11 +461,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the high bay warehouse</t>
+          <t>drilling the workpiece for 15 seconds</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the human workstation</t>
+          <t>moving towards the slot 3</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>194</v>
+        <v>139</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -529,14 +529,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>burning the workpiece for 30 seconds</t>
+          <t>milling the workpiece</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>256</v>
+        <v>106</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -563,14 +563,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the human workstation</t>
+          <t>moving towards the slot 8</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -597,14 +597,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 35 seconds</t>
+          <t>drilling the workpiece for 20 seconds</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -631,14 +631,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 20 seconds</t>
+          <t>drilling the workpiece for 24 seconds</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -665,14 +665,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the oven</t>
+          <t>lowering the workpiece</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -699,14 +699,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 21 seconds</t>
+          <t>dropping off the workpiece at the oven</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -733,20 +733,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>opening the oven door</t>
+          <t>drilling the workpiece for 35 seconds</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>867</v>
+        <v>22</v>
       </c>
       <c r="C10" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -755,32 +755,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.938</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.968</t>
+          <t>1.000</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>burning the workpiece for 25 seconds</t>
+          <t>moving towards the slot 4</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>516</v>
+        <v>65</v>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -789,60 +789,60 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.917</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.957</t>
+          <t>1.000</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 6</t>
+          <t>burning the workpiece for 25 seconds</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>193</v>
+        <v>516</v>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.833</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.800</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.909</t>
+          <t>0.889</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the high bay warehouse</t>
+          <t>moving towards the sink 2</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>360</v>
+        <v>244</v>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -857,202 +857,202 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.778</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.875</t>
+          <t>0.857</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>burning the workpiece for 15 seconds</t>
+          <t>burning the workpiece for 20 seconds</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>451</v>
+        <v>534</v>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.765</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.769</t>
+          <t>0.929</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.870</t>
+          <t>0.839</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>burning the workpiece for 20 seconds</t>
+          <t>transporting the workpiece to the milling_machine</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>534</v>
+        <v>2518</v>
       </c>
       <c r="C15" t="n">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.765</t>
+          <t>0.805</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.805</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.867</t>
+          <t>0.805</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>moving towards the sink 2</t>
+          <t>transporting the workpiece to the pm_1_sink</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>244</v>
+        <v>91</v>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>0.800</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the sink 3</t>
+          <t>temper the workpiece for 40 seconds</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>77</v>
+        <v>1346</v>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.821</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.719</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>0.767</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>temper the workpiece for 40 seconds</t>
+          <t>transporting the workpiece to the punch or drill</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1346</v>
+        <v>746</v>
       </c>
       <c r="C18" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.861</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.756</t>
+          <t>0.619</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.805</t>
+          <t>0.765</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>milling the workpiece</t>
+          <t>burning the workpiece for 15 seconds</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>106</v>
+        <v>451</v>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1061,66 +1061,66 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.615</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>0.762</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the sink 2</t>
+          <t>transporting the bucket to the slot 4</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>70</v>
+        <v>158</v>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.857</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>0.750</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the drilling machine sink</t>
+          <t>opening the oven door</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>296</v>
+        <v>867</v>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1129,270 +1129,270 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.625</t>
+          <t>0.579</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.769</t>
+          <t>0.733</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the light barrier 3</t>
+          <t>UNKNOWN_EVENT</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>404</v>
+        <v>8244</v>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>138</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.798</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.625</t>
+          <t>0.670</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.769</t>
+          <t>0.728</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the oven</t>
+          <t>dropping off the bucket at the slot</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1202</v>
+        <v>2069</v>
       </c>
       <c r="C23" t="n">
         <v>27</v>
       </c>
       <c r="D23" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.794</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.730</t>
+          <t>0.551</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.761</t>
+          <t>0.711</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the milling_machine</t>
+          <t>transporting the workpiece to the drilling machine sink</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2518</v>
+        <v>1297</v>
       </c>
       <c r="C24" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="D24" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.737</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.778</t>
+          <t>0.548</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.757</t>
+          <t>0.708</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ejecting the workpiece to the sink 2</t>
+          <t>transporting the workpiece to the inside of the oven</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>27</v>
+        <v>474</v>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
           <t>0.750</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>0.750</t>
-        </is>
-      </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.706</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>transporting the bucket to the conveyor belt</t>
+          <t>transporting the bucket to the slot 1</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2376</v>
+        <v>326</v>
       </c>
       <c r="C26" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E26" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0.917</t>
+          <t>0.600</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.635</t>
+          <t>0.857</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.706</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 7</t>
+          <t>moving towards the oven</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>143</v>
+        <v>2451</v>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>0.755</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.649</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.698</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the oven</t>
+          <t>transporting the bucket to the high-bay warehouse crane jib</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1627</v>
+        <v>907</v>
       </c>
       <c r="C28" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.966</t>
+          <t>0.867</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.596</t>
+          <t>0.565</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.737</t>
+          <t>0.684</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the drilling machine sink</t>
+          <t>transporting the workpiece to the sink 2</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1297</v>
+        <v>70</v>
       </c>
       <c r="C29" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1401,66 +1401,66 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.581</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>0.735</t>
+          <t>0.667</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>picking up the bucket from the slot</t>
+          <t>transporting the workpiece to the high bay warehouse</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1868</v>
+        <v>173</v>
       </c>
       <c r="C30" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.571</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.574</t>
+          <t>0.800</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.729</t>
+          <t>0.667</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>moving towards the slot 3</t>
+          <t>picking up the workpiece from the high bay warehouse waiting platform</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1469,32 +1469,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.727</t>
+          <t>0.667</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the punch or drill</t>
+          <t>picking up the bucket from the slot</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>746</v>
+        <v>1868</v>
       </c>
       <c r="C32" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1503,168 +1503,168 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.562</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.720</t>
+          <t>0.667</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>UNKNOWN_EVENT</t>
+          <t>burning the workpiece for 30 seconds</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>8244</v>
+        <v>256</v>
       </c>
       <c r="C33" t="n">
-        <v>128</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.790</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.653</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.715</t>
+          <t>0.667</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dropping off the bucket at the slot</t>
+          <t>transporting the workpiece to the oven</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2069</v>
+        <v>1627</v>
       </c>
       <c r="C34" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" t="n">
         <v>21</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.952</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.533</t>
+          <t>0.488</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.696</t>
+          <t>0.645</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>transporting the bucket to the high-bay warehouse crane jib</t>
+          <t>picking up the workpiece from the oven</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>907</v>
+        <v>1202</v>
       </c>
       <c r="C35" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E35" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.875</t>
+          <t>0.650</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.560</t>
+          <t>0.619</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.683</t>
+          <t>0.634</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>moving towards the oven</t>
+          <t>picking up the bucket from the conveyor belt</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2451</v>
+        <v>1832</v>
       </c>
       <c r="C36" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="D36" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E36" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.765</t>
+          <t>0.840</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.672</t>
+          <t>0.627</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>moving towards the slot 2</t>
+          <t>picking up the workpiece from the high bay warehouse</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>95</v>
+        <v>360</v>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1673,172 +1673,172 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.455</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.625</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the initial position</t>
+          <t>transporting the workpiece to the human workstation</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>71</v>
+        <v>924</v>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.765</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.520</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.619</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the high bay warehouse waiting platform</t>
+          <t>transporting the bucket to the conveyor belt</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>150</v>
+        <v>2376</v>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E39" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.900</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.458</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.607</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 3</t>
+          <t>calibrating motor 3</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>257</v>
+        <v>5003</v>
       </c>
       <c r="C40" t="n">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E40" t="n">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0.625</t>
+          <t>0.808</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.714</t>
+          <t>0.480</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.602</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 4</t>
+          <t>transporting the workpiece to the sorting machine</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>158</v>
+        <v>1029</v>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.406</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.578</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>moving towards the slot 8</t>
+          <t>transporting the bucket to the slot 6</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>72</v>
+        <v>193</v>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1848,211 +1848,211 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.571</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>moving towards the slot 6</t>
+          <t>transporting the bucket to the slot 5</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="C43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" t="n">
         <v>3</v>
       </c>
-      <c r="D43" t="n">
-        <v>1</v>
-      </c>
       <c r="E43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.400</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.571</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>calibrating motor 2</t>
+          <t>transporting the bucket to the slot 8</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2036</v>
+        <v>100</v>
       </c>
       <c r="C44" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E44" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.774</t>
+          <t>0.400</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.640</t>
+          <t>0.571</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 0</t>
+          <t>transporting the workpiece to the mill</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>652</v>
+        <v>217</v>
       </c>
       <c r="C45" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D45" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.615</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.615</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.615</t>
+          <t>0.571</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>picking up the bucket from the conveyor belt</t>
+          <t>transporting the workpiece to the dm_2_sink</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1832</v>
+        <v>97</v>
       </c>
       <c r="C46" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0.867</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>0.441</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>0.584</t>
+          <t>0.571</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 1</t>
+          <t>transporting the bucket to the slot 0</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>326</v>
+        <v>652</v>
       </c>
       <c r="C47" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D47" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E47" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0.438</t>
+          <t>0.571</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>0.875</t>
+          <t>0.571</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>0.583</t>
+          <t>0.571</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the drill</t>
+          <t>moving towards the slot 0</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>242</v>
+        <v>551</v>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.889</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.381</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>0.533</t>
         </is>
       </c>
     </row>
@@ -2066,106 +2066,106 @@
         <v>522</v>
       </c>
       <c r="C49" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D49" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0.423</t>
+          <t>0.429</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>0.846</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0.564</t>
+          <t>0.522</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>calibrating motor 3</t>
+          <t>ejecting the workpiece to the sink 2</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>5003</v>
+        <v>27</v>
       </c>
       <c r="C50" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>0.797</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>0.414</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>0.500</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the inside of the oven</t>
+          <t>picking up the workpiece from the drilling machine sink</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>474</v>
+        <v>296</v>
       </c>
       <c r="C51" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D51" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
           <t>0.500</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>0.545</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>0.522</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the sink 3</t>
+          <t>dropping off the workpiece at the high bay warehouse</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C52" t="n">
         <v>1</v>
@@ -2195,29 +2195,29 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 2</t>
+          <t>moving towards the slot 2</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>124</v>
+        <v>95</v>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2229,29 +2229,29 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the human workstation</t>
+          <t>dropping off the workpiece at the human workstation</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>924</v>
+        <v>53</v>
       </c>
       <c r="C54" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2263,527 +2263,527 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the pm_1_sink</t>
+          <t>calibrating motor 2</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>91</v>
+        <v>2036</v>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="D55" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E55" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.720</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.327</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.450</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 9 seconds</t>
+          <t>transporting the bucket to the slot 2</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>18</v>
+        <v>124</v>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E56" t="n">
         <v>2</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.400</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.444</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>moving towards the slot 0</t>
+          <t>transporting the workpiece to the light barrier 3</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>551</v>
+        <v>404</v>
       </c>
       <c r="C57" t="n">
         <v>3</v>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>0.273</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.429</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>transporting the bucket to the high bay warehouse crane jib</t>
+          <t>transporting the bucket to the vacuum gripper robot crane jib</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>159</v>
+        <v>270</v>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D58" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E58" t="n">
         <v>1</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.286</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.857</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.429</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the sorting machine</t>
+          <t>transporting the bucket to the slot 3</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1029</v>
+        <v>257</v>
       </c>
       <c r="C59" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E59" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>0.321</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>0.486</t>
+          <t>0.429</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>transporting the bucket to the vacuum gripper robot crane jib</t>
+          <t>transporting the workpiece to the punch</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>270</v>
+        <v>350</v>
       </c>
       <c r="C60" t="n">
+        <v>4</v>
+      </c>
+      <c r="D60" t="n">
+        <v>4</v>
+      </c>
+      <c r="E60" t="n">
         <v>7</v>
       </c>
-      <c r="D60" t="n">
-        <v>14</v>
-      </c>
-      <c r="E60" t="n">
-        <v>3</v>
-      </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>0.700</t>
+          <t>0.364</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>0.452</t>
+          <t>0.421</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the mill</t>
+          <t>transporting the workpiece to the high bay warehouse waiting platform</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>217</v>
+        <v>191</v>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.250</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
           <t>0.333</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>0.444</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>moving towards the sink 3</t>
+          <t>transporting the bucket to the high bay warehouse crane jib</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>190</v>
+        <v>159</v>
       </c>
       <c r="C62" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E62" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.250</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>0.556</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>0.435</t>
+          <t>0.286</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the high bay warehouse</t>
+          <t>ejecting the workpiece to the conveyor belt</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>173</v>
+        <v>113</v>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D63" t="n">
         <v>3</v>
       </c>
       <c r="E63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.250</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.286</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the ejection position</t>
+          <t>transporting the workpiece to the drill</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>110</v>
+        <v>242</v>
       </c>
       <c r="C64" t="n">
         <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.167</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.286</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>moving towards the slot 1</t>
+          <t>moving towards the sink 3</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>163</v>
+        <v>190</v>
       </c>
       <c r="C65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E65" t="n">
         <v>4</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>0.300</t>
+          <t>0.100</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>0.429</t>
+          <t>0.200</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>0.353</t>
+          <t>0.133</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the high bay warehouse waiting platform</t>
+          <t>moving towards the sink 1</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>191</v>
+        <v>31</v>
       </c>
       <c r="C66" t="n">
         <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="E66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.045</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.087</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 5</t>
+          <t>transporting the bucket to the slot 7</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the punch</t>
+          <t>moving towards the slot 5</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>350</v>
+        <v>71</v>
       </c>
       <c r="C68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E68" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>moving towards the sink 1</t>
+          <t>moving towards the slot 6</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="C69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E69" t="n">
         <v>0</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>0.160</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 8</t>
+          <t>picking up the workpiece from the sink 1</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
@@ -2820,7 +2820,7 @@
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -2841,11 +2841,11 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ejecting the workpiece to the conveyor belt</t>
+          <t>moving towards the slot 7</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>113</v>
+        <v>50</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
@@ -2854,7 +2854,7 @@
         <v>3</v>
       </c>
       <c r="E72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -2875,17 +2875,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 6 seconds</t>
+          <t>ejecting the workpiece to the sink 1</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
@@ -2909,20 +2909,20 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 24 seconds</t>
+          <t>transporting the workpiece to the ejection position</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>26</v>
+        <v>110</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -2943,17 +2943,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the sorting machine conveyor belt</t>
+          <t>picking up the workpiece from the sink 3</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E75" t="n">
         <v>0</v>
@@ -2977,20 +2977,20 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the sorting machine conveyor belt</t>
+          <t>transporting the workpiece to the sink 3</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -3011,20 +3011,20 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>moving towards the slot 4</t>
+          <t>moving towards the slot 1</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>65</v>
+        <v>163</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -3113,20 +3113,20 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the sink 2</t>
+          <t>moving towards the punching machine sink</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -3147,20 +3147,20 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 30 seconds</t>
+          <t>transporting the workpiece to the sorting machine conveyor belt</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -3181,17 +3181,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ejecting the workpiece to the sink 1</t>
+          <t>drilling the workpiece for 6 seconds</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
@@ -3215,20 +3215,20 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the high bay warehouse waiting platform</t>
+          <t>picking up the workpiece from the sink 2</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -3249,20 +3249,20 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the dm_2_sink</t>
+          <t>dropping off the workpiece at the high bay warehouse waiting platform</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>97</v>
+        <v>46</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -3283,11 +3283,11 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 3 seconds</t>
+          <t>transporting the workpiece to the initial position</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
@@ -3296,7 +3296,7 @@
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -3317,20 +3317,20 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>moving towards the slot 5</t>
+          <t>dropping off the workpiece at the sorting machine conveyor belt</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>71</v>
+        <v>3</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -3343,108 +3343,6 @@
         </is>
       </c>
       <c r="H86" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>moving towards the slot 7</t>
-        </is>
-      </c>
-      <c r="B87" t="n">
-        <v>50</v>
-      </c>
-      <c r="C87" t="n">
-        <v>0</v>
-      </c>
-      <c r="D87" t="n">
-        <v>3</v>
-      </c>
-      <c r="E87" t="n">
-        <v>0</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>picking up the workpiece from the sink 1</t>
-        </is>
-      </c>
-      <c r="B88" t="n">
-        <v>6</v>
-      </c>
-      <c r="C88" t="n">
-        <v>0</v>
-      </c>
-      <c r="D88" t="n">
-        <v>4</v>
-      </c>
-      <c r="E88" t="n">
-        <v>0</v>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>moving towards the punching machine sink</t>
-        </is>
-      </c>
-      <c r="B89" t="n">
-        <v>3</v>
-      </c>
-      <c r="C89" t="n">
-        <v>0</v>
-      </c>
-      <c r="D89" t="n">
-        <v>3</v>
-      </c>
-      <c r="E89" t="n">
-        <v>0</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
         <is>
           <t>0.000</t>
         </is>

--- a/tables/autoencoder_per_event_metrics.xlsx
+++ b/tables/autoencoder_per_event_metrics.xlsx
@@ -461,11 +461,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 15 seconds</t>
+          <t>moving towards the slot 8</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>moving towards the slot 3</t>
+          <t>drilling the workpiece for 35 seconds</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>139</v>
+        <v>22</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -529,14 +529,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>milling the workpiece</t>
+          <t>drilling the workpiece for 20 seconds</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>106</v>
+        <v>30</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -563,14 +563,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>moving towards the slot 8</t>
+          <t>milling the workpiece</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -597,14 +597,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 20 seconds</t>
+          <t>dropping off the workpiece at the oven</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -631,11 +631,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 24 seconds</t>
+          <t>lowering the workpiece</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
@@ -665,11 +665,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lowering the workpiece</t>
+          <t>drilling the workpiece for 24 seconds</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
@@ -699,14 +699,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the oven</t>
+          <t>moving towards the slot 4</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -733,11 +733,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 35 seconds</t>
+          <t>drilling the workpiece for 15 seconds</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
@@ -767,14 +767,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>moving towards the slot 4</t>
+          <t>moving towards the slot 3</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>65</v>
+        <v>139</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -1379,11 +1379,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the sink 2</t>
+          <t>burning the workpiece for 30 seconds</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>70</v>
+        <v>256</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
@@ -1413,29 +1413,29 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the high bay warehouse</t>
+          <t>picking up the bucket from the slot</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>173</v>
+        <v>1868</v>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1447,20 +1447,20 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the high bay warehouse waiting platform</t>
+          <t>transporting the workpiece to the sink 2</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1481,20 +1481,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>picking up the bucket from the slot</t>
+          <t>picking up the workpiece from the high bay warehouse waiting platform</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1868</v>
+        <v>150</v>
       </c>
       <c r="C32" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1515,29 +1515,29 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>burning the workpiece for 30 seconds</t>
+          <t>transporting the workpiece to the high bay warehouse</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>256</v>
+        <v>173</v>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E33" t="n">
         <v>1</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.571</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.800</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1855,29 +1855,29 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 5</t>
+          <t>transporting the workpiece to the mill</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>101</v>
+        <v>217</v>
       </c>
       <c r="C43" t="n">
         <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -1923,11 +1923,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the mill</t>
+          <t>transporting the workpiece to the dm_2_sink</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>217</v>
+        <v>97</v>
       </c>
       <c r="C45" t="n">
         <v>2</v>
@@ -1957,29 +1957,29 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the dm_2_sink</t>
+          <t>transporting the bucket to the slot 5</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C46" t="n">
         <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.400</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2093,29 +2093,29 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ejecting the workpiece to the sink 2</t>
+          <t>moving towards the slot 2</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>27</v>
+        <v>95</v>
       </c>
       <c r="C50" t="n">
         <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2161,29 +2161,29 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the high bay warehouse</t>
+          <t>dropping off the workpiece at the human workstation</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="C52" t="n">
         <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2195,29 +2195,29 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>moving towards the slot 2</t>
+          <t>ejecting the workpiece to the sink 2</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>95</v>
+        <v>27</v>
       </c>
       <c r="C53" t="n">
         <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2229,29 +2229,29 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the human workstation</t>
+          <t>dropping off the workpiece at the high bay warehouse</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="C54" t="n">
         <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2331,29 +2331,29 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the light barrier 3</t>
+          <t>transporting the bucket to the vacuum gripper robot crane jib</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>404</v>
+        <v>270</v>
       </c>
       <c r="C57" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E57" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.286</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>0.857</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2365,29 +2365,29 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>transporting the bucket to the vacuum gripper robot crane jib</t>
+          <t>transporting the bucket to the slot 3</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="C58" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D58" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2399,29 +2399,29 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 3</t>
+          <t>transporting the workpiece to the light barrier 3</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>257</v>
+        <v>404</v>
       </c>
       <c r="C59" t="n">
         <v>3</v>
       </c>
       <c r="D59" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>0.273</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2501,11 +2501,11 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>transporting the bucket to the high bay warehouse crane jib</t>
+          <t>ejecting the workpiece to the conveyor belt</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="C62" t="n">
         <v>1</v>
@@ -2535,11 +2535,11 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ejecting the workpiece to the conveyor belt</t>
+          <t>transporting the bucket to the high bay warehouse crane jib</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>113</v>
+        <v>159</v>
       </c>
       <c r="C63" t="n">
         <v>1</v>
@@ -2671,20 +2671,20 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 7</t>
+          <t>ejecting the workpiece to the sink 1</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>143</v>
+        <v>4</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -2705,17 +2705,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>moving towards the slot 5</t>
+          <t>moving towards the punching machine sink</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>71</v>
+        <v>3</v>
       </c>
       <c r="C68" t="n">
         <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E68" t="n">
         <v>0</v>
@@ -2739,17 +2739,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>moving towards the slot 6</t>
+          <t>dropping off the workpiece at the sorting machine conveyor belt</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>110</v>
+        <v>3</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E69" t="n">
         <v>0</v>
@@ -2773,20 +2773,20 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the sink 1</t>
+          <t>picking up the workpiece from the punching machine sink</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>6</v>
+        <v>83</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -2841,20 +2841,20 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>moving towards the slot 7</t>
+          <t>transporting the workpiece to the ejection position</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -2875,20 +2875,20 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ejecting the workpiece to the sink 1</t>
+          <t>transporting the bucket to the slot 7</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>4</v>
+        <v>143</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -2909,17 +2909,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the ejection position</t>
+          <t>transporting the workpiece to the initial position</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E74" t="n">
         <v>2</v>
@@ -2943,20 +2943,20 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the sink 3</t>
+          <t>moving towards the slot 1</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>46</v>
+        <v>163</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -2977,20 +2977,20 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the sink 3</t>
+          <t>picking up the workpiece from the sink 3</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -3011,20 +3011,20 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>moving towards the slot 1</t>
+          <t>picking up the workpiece from the sink 1</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>163</v>
+        <v>6</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -3045,20 +3045,20 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ejecting the workpiece to the sink 3</t>
+          <t>transporting the workpiece to the sink 3</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>29</v>
+        <v>77</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -3079,20 +3079,20 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the punching machine sink</t>
+          <t>moving towards the slot 7</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -3113,17 +3113,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>moving towards the punching machine sink</t>
+          <t>ejecting the workpiece to the sink 3</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
@@ -3147,20 +3147,20 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the sorting machine conveyor belt</t>
+          <t>moving towards the slot 5</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -3181,20 +3181,20 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 6 seconds</t>
+          <t>transporting the workpiece to the sorting machine conveyor belt</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -3215,20 +3215,20 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the sink 2</t>
+          <t>dropping off the workpiece at the high bay warehouse waiting platform</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -3249,20 +3249,20 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the high bay warehouse waiting platform</t>
+          <t>moving towards the slot 6</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>46</v>
+        <v>110</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -3283,20 +3283,20 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the initial position</t>
+          <t>picking up the workpiece from the sink 2</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -3317,17 +3317,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the sorting machine conveyor belt</t>
+          <t>drilling the workpiece for 6 seconds</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E86" t="n">
         <v>0</v>

--- a/tables/autoencoder_per_event_metrics.xlsx
+++ b/tables/autoencoder_per_event_metrics.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H86"/>
+  <dimension ref="A1:H90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,14 +461,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>moving towards the slot 8</t>
+          <t>dropping off the workpiece at the oven</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -495,11 +495,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 35 seconds</t>
+          <t>moving towards the slot 8</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
@@ -529,11 +529,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 20 seconds</t>
+          <t>drilling the workpiece for 15 seconds</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
@@ -563,14 +563,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>milling the workpiece</t>
+          <t>drilling the workpiece for 35 seconds</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>106</v>
+        <v>22</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -597,14 +597,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the oven</t>
+          <t>lowering the workpiece</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -631,14 +631,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>lowering the workpiece</t>
+          <t>moving towards the slot 3</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>38</v>
+        <v>139</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -665,14 +665,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 24 seconds</t>
+          <t>milling the workpiece</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -699,11 +699,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>moving towards the slot 4</t>
+          <t>drilling the workpiece for 24 seconds</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
@@ -733,11 +733,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 15 seconds</t>
+          <t>drilling the workpiece for 20 seconds</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
@@ -767,20 +767,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>moving towards the slot 3</t>
+          <t>burning the workpiece for 25 seconds</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>139</v>
+        <v>516</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -789,23 +789,23 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.800</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.889</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>burning the workpiece for 25 seconds</t>
+          <t>picking up the workpiece from the high bay warehouse</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>516</v>
+        <v>360</v>
       </c>
       <c r="C12" t="n">
         <v>8</v>
@@ -814,7 +814,7 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -823,202 +823,202 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>0.727</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.889</t>
+          <t>0.842</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>moving towards the sink 2</t>
+          <t>burning the workpiece for 20 seconds</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>244</v>
+        <v>534</v>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.765</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.929</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>0.839</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>burning the workpiece for 20 seconds</t>
+          <t>transporting the workpiece to the punch or drill</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>534</v>
+        <v>746</v>
       </c>
       <c r="C14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.765</t>
+          <t>0.938</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.929</t>
+          <t>0.714</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.839</t>
+          <t>0.811</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the milling_machine</t>
+          <t>transporting the workpiece to the sorting machine</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2518</v>
+        <v>1029</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="D15" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.805</t>
+          <t>0.920</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.805</t>
+          <t>0.719</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.805</t>
+          <t>0.807</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the pm_1_sink</t>
+          <t>transporting the workpiece to the milling_machine</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>91</v>
+        <v>2518</v>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.833</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.779</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>0.805</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>temper the workpiece for 40 seconds</t>
+          <t>transporting the workpiece to the pm_1_sink</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1346</v>
+        <v>91</v>
       </c>
       <c r="C17" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.821</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.719</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.767</t>
+          <t>0.800</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the punch or drill</t>
+          <t>transporting the workpiece to the drilling machine sink</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>746</v>
+        <v>1297</v>
       </c>
       <c r="C18" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1027,100 +1027,100 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.619</t>
+          <t>0.645</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.765</t>
+          <t>0.784</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>burning the workpiece for 15 seconds</t>
+          <t>temper the workpiece for 40 seconds</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>451</v>
+        <v>1346</v>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.781</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.615</t>
+          <t>0.781</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.762</t>
+          <t>0.781</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 4</t>
+          <t>opening the oven door</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>158</v>
+        <v>867</v>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>0.632</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.774</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>opening the oven door</t>
+          <t>burning the workpiece for 15 seconds</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>867</v>
+        <v>451</v>
       </c>
       <c r="C21" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1129,284 +1129,284 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.579</t>
+          <t>0.615</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.733</t>
+          <t>0.762</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>UNKNOWN_EVENT</t>
+          <t>transporting the workpiece to the mill</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>8244</v>
+        <v>217</v>
       </c>
       <c r="C22" t="n">
-        <v>138</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.798</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.670</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.728</t>
+          <t>0.750</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>dropping off the bucket at the slot</t>
+          <t>transporting the bucket to the slot 4</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2069</v>
+        <v>158</v>
       </c>
       <c r="C23" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>0.857</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.711</t>
+          <t>0.750</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the drilling machine sink</t>
+          <t>UNKNOWN_EVENT</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1297</v>
+        <v>8244</v>
       </c>
       <c r="C24" t="n">
-        <v>17</v>
+        <v>134</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="E24" t="n">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.859</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.548</t>
+          <t>0.650</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.708</t>
+          <t>0.740</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the inside of the oven</t>
+          <t>transporting the workpiece to the oven</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>474</v>
+        <v>1627</v>
       </c>
       <c r="C25" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.960</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.585</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.706</t>
+          <t>0.727</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 1</t>
+          <t>moving towards the oven</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>326</v>
+        <v>2451</v>
       </c>
       <c r="C26" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="D26" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>0.970</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>0.561</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.706</t>
+          <t>0.711</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>moving towards the oven</t>
+          <t>dropping off the bucket at the slot</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2451</v>
+        <v>2069</v>
       </c>
       <c r="C27" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D27" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.755</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.649</t>
+          <t>0.551</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.698</t>
+          <t>0.711</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>transporting the bucket to the high-bay warehouse crane jib</t>
+          <t>picking up the workpiece from the oven</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>907</v>
+        <v>1202</v>
       </c>
       <c r="C28" t="n">
         <v>13</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.867</t>
+          <t>0.812</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.565</t>
+          <t>0.619</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.684</t>
+          <t>0.703</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>burning the workpiece for 30 seconds</t>
+          <t>transporting the bucket to the high-bay warehouse crane jib</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>256</v>
+        <v>907</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.867</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.565</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.684</t>
         </is>
       </c>
     </row>
@@ -1420,56 +1420,56 @@
         <v>1868</v>
       </c>
       <c r="C30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.963</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.520</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.675</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the sink 2</t>
+          <t>moving towards the slot 4</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C31" t="n">
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1515,29 +1515,29 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the high bay warehouse</t>
+          <t>transporting the workpiece to the sink 3</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>173</v>
+        <v>77</v>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1549,351 +1549,351 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the oven</t>
+          <t>burning the workpiece for 30 seconds</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1627</v>
+        <v>256</v>
       </c>
       <c r="C34" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.952</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.488</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.645</t>
+          <t>0.667</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the oven</t>
+          <t>dropping off the workpiece at the drilling machine sink</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="C35" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.650</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.619</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.634</t>
+          <t>0.667</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>picking up the bucket from the conveyor belt</t>
+          <t>transporting the workpiece to the human workstation</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1832</v>
+        <v>924</v>
       </c>
       <c r="C36" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D36" t="n">
         <v>4</v>
       </c>
       <c r="E36" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.840</t>
+          <t>0.778</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.560</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.627</t>
+          <t>0.651</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the high bay warehouse</t>
+          <t>transporting the bucket to the slot 1</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>360</v>
+        <v>326</v>
       </c>
       <c r="C37" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E37" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.455</t>
+          <t>0.929</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.625</t>
+          <t>0.650</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the human workstation</t>
+          <t>transporting the workpiece to the inside of the oven</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>924</v>
+        <v>474</v>
       </c>
       <c r="C38" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D38" t="n">
+        <v>9</v>
+      </c>
+      <c r="E38" t="n">
         <v>4</v>
       </c>
-      <c r="E38" t="n">
-        <v>12</v>
-      </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.765</t>
+          <t>0.571</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0.520</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.619</t>
+          <t>0.649</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>transporting the bucket to the conveyor belt</t>
+          <t>transporting the workpiece to the light barrier 3</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2376</v>
+        <v>404</v>
       </c>
       <c r="C39" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.900</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.458</t>
+          <t>0.455</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.607</t>
+          <t>0.625</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>calibrating motor 3</t>
+          <t>transporting the workpiece to the high bay warehouse</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>5003</v>
+        <v>173</v>
       </c>
       <c r="C40" t="n">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="D40" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E40" t="n">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0.808</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.480</t>
+          <t>0.800</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0.602</t>
+          <t>0.615</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the sorting machine</t>
+          <t>picking up the bucket from the conveyor belt</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1029</v>
+        <v>1832</v>
       </c>
       <c r="C41" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E41" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.778</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.406</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.578</t>
+          <t>0.609</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 6</t>
+          <t>calibrating motor 3</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>193</v>
+        <v>5003</v>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="E42" t="n">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.714</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.528</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>0.607</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the mill</t>
+          <t>transporting the bucket to the conveyor belt</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>217</v>
+        <v>2376</v>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E43" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.818</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.458</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>0.587</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 8</t>
+          <t>transporting the bucket to the slot 5</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C44" t="n">
         <v>2</v>
@@ -1957,11 +1957,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 5</t>
+          <t>transporting the bucket to the slot 8</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C46" t="n">
         <v>2</v>
@@ -2001,155 +2001,155 @@
         <v>8</v>
       </c>
       <c r="D47" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E47" t="n">
         <v>6</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
+          <t>0.533</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
           <t>0.571</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>0.571</t>
-        </is>
-      </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>0.552</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>moving towards the slot 0</t>
+          <t>transporting the workpiece to the punch</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>551</v>
+        <v>350</v>
       </c>
       <c r="C48" t="n">
+        <v>7</v>
+      </c>
+      <c r="D48" t="n">
         <v>8</v>
       </c>
-      <c r="D48" t="n">
-        <v>1</v>
-      </c>
       <c r="E48" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>0.889</t>
+          <t>0.467</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>0.381</t>
+          <t>0.636</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>0.533</t>
+          <t>0.538</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the outside of the oven</t>
+          <t>moving towards the slot 0</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>522</v>
+        <v>551</v>
       </c>
       <c r="C49" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D49" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0.429</t>
+          <t>0.889</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.381</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0.522</t>
+          <t>0.533</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>moving towards the slot 2</t>
+          <t>transporting the workpiece to the outside of the oven</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>95</v>
+        <v>522</v>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E50" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.414</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.511</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the drilling machine sink</t>
+          <t>transporting the workpiece to the ejection position</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>296</v>
+        <v>110</v>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2161,11 +2161,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the human workstation</t>
+          <t>moving towards the slot 2</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="C52" t="n">
         <v>1</v>
@@ -2195,20 +2195,20 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ejecting the workpiece to the sink 2</t>
+          <t>transporting the bucket to the slot 6</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>27</v>
+        <v>193</v>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -2229,11 +2229,11 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the high bay warehouse</t>
+          <t>transporting the workpiece to the sink 2</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="C54" t="n">
         <v>1</v>
@@ -2263,190 +2263,190 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>calibrating motor 2</t>
+          <t>picking up the workpiece from the drilling machine sink</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2036</v>
+        <v>296</v>
       </c>
       <c r="C55" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D55" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>0.720</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>0.327</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>0.450</t>
+          <t>0.500</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 2</t>
+          <t>dropping off the workpiece at the human workstation</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>124</v>
+        <v>53</v>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
         <v>2</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
           <t>0.500</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>0.444</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>transporting the bucket to the vacuum gripper robot crane jib</t>
+          <t>ejecting the workpiece to the conveyor belt</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>270</v>
+        <v>113</v>
       </c>
       <c r="C57" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D57" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>0.300</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>0.429</t>
+          <t>0.462</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 3</t>
+          <t>ejecting the workpiece to the sink 2</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>257</v>
+        <v>27</v>
       </c>
       <c r="C58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D58" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E58" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.286</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>0.429</t>
+          <t>0.444</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the light barrier 3</t>
+          <t>transporting the bucket to the slot 2</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>404</v>
+        <v>124</v>
       </c>
       <c r="C59" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" t="n">
         <v>3</v>
       </c>
-      <c r="D59" t="n">
-        <v>0</v>
-      </c>
       <c r="E59" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.400</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>0.429</t>
+          <t>0.444</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the punch</t>
+          <t>transporting the bucket to the slot 3</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>350</v>
+        <v>257</v>
       </c>
       <c r="C60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E60" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -2455,372 +2455,372 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>0.364</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>0.421</t>
+          <t>0.429</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the high bay warehouse waiting platform</t>
+          <t>calibrating motor 2</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>191</v>
+        <v>2036</v>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D61" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E61" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.528</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.345</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.418</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ejecting the workpiece to the conveyor belt</t>
+          <t>dropping off the workpiece at the high bay warehouse</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>113</v>
+        <v>38</v>
       </c>
       <c r="C62" t="n">
         <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>0.400</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>transporting the bucket to the high bay warehouse crane jib</t>
+          <t>transporting the bucket to the vacuum gripper robot crane jib</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>159</v>
+        <v>270</v>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D63" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.231</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.857</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>0.364</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the drill</t>
+          <t>moving towards the sink 2</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E64" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.240</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>0.364</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>moving towards the sink 3</t>
+          <t>dropping off the workpiece at the high bay warehouse waiting platform</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>190</v>
+        <v>46</v>
       </c>
       <c r="C65" t="n">
         <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E65" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>0.100</t>
+          <t>0.250</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>0.200</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.333</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>moving towards the sink 1</t>
+          <t>transporting the workpiece to the high bay warehouse waiting platform</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="C66" t="n">
         <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>0.250</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0.333</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ejecting the workpiece to the sink 1</t>
+          <t>transporting the bucket to the high bay warehouse crane jib</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>4</v>
+        <v>159</v>
       </c>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.250</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.286</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>moving towards the punching machine sink</t>
+          <t>transporting the workpiece to the drill</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>3</v>
+        <v>242</v>
       </c>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.167</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.286</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the sorting machine conveyor belt</t>
+          <t>moving towards the sink 3</t>
         </is>
       </c>
       <c r="B69" t="n">
+        <v>190</v>
+      </c>
+      <c r="C69" t="n">
+        <v>2</v>
+      </c>
+      <c r="D69" t="n">
+        <v>10</v>
+      </c>
+      <c r="E69" t="n">
         <v>3</v>
       </c>
-      <c r="C69" t="n">
-        <v>0</v>
-      </c>
-      <c r="D69" t="n">
-        <v>3</v>
-      </c>
-      <c r="E69" t="n">
-        <v>0</v>
-      </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.167</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.400</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.235</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the punching machine sink</t>
+          <t>moving towards the sink 1</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>83</v>
+        <v>31</v>
       </c>
       <c r="C70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.040</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.077</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the drilling machine sink</t>
+          <t>transporting the workpiece to the light barrier 1</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -2841,11 +2841,11 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the ejection position</t>
+          <t>transporting the workpiece to the initial position</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
@@ -2875,20 +2875,20 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 7</t>
+          <t>picking up the workpiece from the punching machine sink</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the initial position</t>
+          <t>moving towards the slot 5</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -2919,10 +2919,10 @@
         <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -2943,20 +2943,20 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>moving towards the slot 1</t>
+          <t>ejecting the workpiece to the sink 1</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>163</v>
+        <v>4</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -2977,11 +2977,11 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the sink 3</t>
+          <t>drilling the workpiece for 3 seconds</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
@@ -3011,17 +3011,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the sink 1</t>
+          <t>moving towards the slot 6</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>6</v>
+        <v>110</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
@@ -3045,20 +3045,20 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the sink 3</t>
+          <t>transporting the bucket to the slot 7</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>77</v>
+        <v>143</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -3079,17 +3079,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>moving towards the slot 7</t>
+          <t>picking up the workpiece from the sink 3</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
@@ -3113,17 +3113,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ejecting the workpiece to the sink 3</t>
+          <t>drilling the workpiece for 6 seconds</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
@@ -3147,17 +3147,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>moving towards the slot 5</t>
+          <t>moving towards the slot 7</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E81" t="n">
         <v>0</v>
@@ -3181,20 +3181,20 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the sorting machine conveyor belt</t>
+          <t>moving towards the punching machine sink</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -3215,20 +3215,20 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the high bay warehouse waiting platform</t>
+          <t>ejecting the workpiece to the sink 3</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -3249,20 +3249,20 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>moving towards the slot 6</t>
+          <t>transporting the workpiece to the sorting machine conveyor belt</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -3283,17 +3283,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the sink 2</t>
+          <t>drilling the workpiece for 4 seconds</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E85" t="n">
         <v>0</v>
@@ -3317,32 +3317,168 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 6 seconds</t>
+          <t>dropping off the workpiece at the sorting machine conveyor belt</t>
         </is>
       </c>
       <c r="B86" t="n">
+        <v>3</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" t="n">
+        <v>3</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>picking up the workpiece from the sink 1</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
         <v>6</v>
       </c>
-      <c r="C86" t="n">
-        <v>0</v>
-      </c>
-      <c r="D86" t="n">
-        <v>6</v>
-      </c>
-      <c r="E86" t="n">
-        <v>0</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
+      <c r="C87" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" t="n">
+        <v>4</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>picking up the workpiece from the sink 2</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>60</v>
+      </c>
+      <c r="C88" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" t="n">
+        <v>2</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>moving towards the slot 1</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>163</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" t="n">
+        <v>9</v>
+      </c>
+      <c r="E89" t="n">
+        <v>2</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>picking up the workpiece from the human workstation</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>194</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
         <is>
           <t>0.000</t>
         </is>

--- a/tables/autoencoder_per_event_metrics.xlsx
+++ b/tables/autoencoder_per_event_metrics.xlsx
@@ -424,7 +424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Val Rows</t>
+          <t>Zeilen gesamt</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -461,14 +461,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the oven</t>
+          <t>drilling the workpiece for 24 seconds</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>82</v>
+        <v>26</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -495,11 +495,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>moving towards the slot 8</t>
+          <t>drilling the workpiece for 15 seconds</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
@@ -529,14 +529,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 15 seconds</t>
+          <t>dropping off the workpiece at the oven</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -563,11 +563,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 35 seconds</t>
+          <t>lowering the workpiece</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
@@ -597,14 +597,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>lowering the workpiece</t>
+          <t>milling the workpiece</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38</v>
+        <v>106</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -631,14 +631,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>moving towards the slot 3</t>
+          <t>drilling the workpiece for 20 seconds</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>139</v>
+        <v>30</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -665,14 +665,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>milling the workpiece</t>
+          <t>drilling the workpiece for 35 seconds</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>22</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -699,14 +699,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 24 seconds</t>
+          <t>moving towards the slot 3</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>139</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -733,11 +733,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 20 seconds</t>
+          <t>moving towards the slot 8</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
@@ -1141,29 +1141,29 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the mill</t>
+          <t>transporting the bucket to the slot 4</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>217</v>
+        <v>158</v>
       </c>
       <c r="C22" t="n">
+        <v>6</v>
+      </c>
+      <c r="D22" t="n">
         <v>3</v>
       </c>
-      <c r="D22" t="n">
-        <v>1</v>
-      </c>
       <c r="E22" t="n">
         <v>1</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.857</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1175,29 +1175,29 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 4</t>
+          <t>transporting the workpiece to the mill</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>158</v>
+        <v>217</v>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1447,29 +1447,29 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>moving towards the slot 4</t>
+          <t>picking up the workpiece from the high bay warehouse waiting platform</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
           <t>0.500</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>1.000</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1481,20 +1481,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the high bay warehouse waiting platform</t>
+          <t>burning the workpiece for 30 seconds</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>150</v>
+        <v>256</v>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1515,29 +1515,29 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the sink 3</t>
+          <t>dropping off the workpiece at the drilling machine sink</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="C33" t="n">
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
           <t>0.500</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>1.000</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1549,29 +1549,29 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>burning the workpiece for 30 seconds</t>
+          <t>moving towards the slot 4</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>256</v>
+        <v>65</v>
       </c>
       <c r="C34" t="n">
         <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1583,29 +1583,29 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the drilling machine sink</t>
+          <t>transporting the workpiece to the sink 3</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="C35" t="n">
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1889,29 +1889,29 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 5</t>
+          <t>transporting the workpiece to the dm_2_sink</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C44" t="n">
         <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -1923,29 +1923,29 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the dm_2_sink</t>
+          <t>transporting the bucket to the slot 8</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C45" t="n">
         <v>2</v>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.400</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -1957,11 +1957,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 8</t>
+          <t>transporting the bucket to the slot 5</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C46" t="n">
         <v>2</v>
@@ -2127,29 +2127,29 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the ejection position</t>
+          <t>dropping off the workpiece at the human workstation</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="C51" t="n">
         <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2161,29 +2161,29 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>moving towards the slot 2</t>
+          <t>transporting the bucket to the slot 6</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>95</v>
+        <v>193</v>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E52" t="n">
         <v>2</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2195,29 +2195,29 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 6</t>
+          <t>picking up the workpiece from the drilling machine sink</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>193</v>
+        <v>296</v>
       </c>
       <c r="C53" t="n">
         <v>2</v>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2229,11 +2229,11 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the sink 2</t>
+          <t>transporting the workpiece to the ejection position</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="C54" t="n">
         <v>1</v>
@@ -2263,29 +2263,29 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the drilling machine sink</t>
+          <t>transporting the workpiece to the sink 2</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>296</v>
+        <v>70</v>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2297,11 +2297,11 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the human workstation</t>
+          <t>moving towards the slot 2</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="C56" t="n">
         <v>1</v>
@@ -2603,11 +2603,11 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the high bay warehouse waiting platform</t>
+          <t>transporting the workpiece to the high bay warehouse waiting platform</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>46</v>
+        <v>191</v>
       </c>
       <c r="C65" t="n">
         <v>1</v>
@@ -2637,11 +2637,11 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the high bay warehouse waiting platform</t>
+          <t>dropping off the workpiece at the high bay warehouse waiting platform</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>191</v>
+        <v>46</v>
       </c>
       <c r="C66" t="n">
         <v>1</v>
@@ -2807,17 +2807,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the light barrier 1</t>
+          <t>moving towards the slot 5</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E71" t="n">
         <v>0</v>
@@ -2841,20 +2841,20 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the initial position</t>
+          <t>ejecting the workpiece to the sink 3</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>71</v>
+        <v>29</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -2875,20 +2875,20 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the punching machine sink</t>
+          <t>ejecting the workpiece to the sink 1</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>83</v>
+        <v>4</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -2909,17 +2909,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>moving towards the slot 5</t>
+          <t>picking up the workpiece from the sink 3</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E74" t="n">
         <v>0</v>
@@ -2943,20 +2943,20 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ejecting the workpiece to the sink 1</t>
+          <t>moving towards the slot 1</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>4</v>
+        <v>163</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -2977,20 +2977,20 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 3 seconds</t>
+          <t>picking up the workpiece from the punching machine sink</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -3011,11 +3011,11 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>moving towards the slot 6</t>
+          <t>transporting the workpiece to the initial position</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
@@ -3024,7 +3024,7 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -3045,20 +3045,20 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 7</t>
+          <t>moving towards the slot 6</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>143</v>
+        <v>110</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -3079,17 +3079,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the sink 3</t>
+          <t>moving towards the punching machine sink</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
@@ -3113,11 +3113,11 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 6 seconds</t>
+          <t>transporting the workpiece to the sorting machine conveyor belt</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
@@ -3126,7 +3126,7 @@
         <v>6</v>
       </c>
       <c r="E80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -3147,17 +3147,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>moving towards the slot 7</t>
+          <t>picking up the workpiece from the human workstation</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>50</v>
+        <v>194</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E81" t="n">
         <v>0</v>
@@ -3181,17 +3181,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>moving towards the punching machine sink</t>
+          <t>drilling the workpiece for 4 seconds</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
@@ -3215,17 +3215,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ejecting the workpiece to the sink 3</t>
+          <t>picking up the workpiece from the sink 1</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
@@ -3249,7 +3249,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the sorting machine conveyor belt</t>
+          <t>moving towards the slot 7</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -3259,10 +3259,10 @@
         <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -3283,17 +3283,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 4 seconds</t>
+          <t>picking up the workpiece from the sink 2</t>
         </is>
       </c>
       <c r="B85" t="n">
+        <v>60</v>
+      </c>
+      <c r="C85" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" t="n">
         <v>2</v>
-      </c>
-      <c r="C85" t="n">
-        <v>0</v>
-      </c>
-      <c r="D85" t="n">
-        <v>1</v>
       </c>
       <c r="E85" t="n">
         <v>0</v>
@@ -3317,20 +3317,20 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the sorting machine conveyor belt</t>
+          <t>transporting the bucket to the slot 7</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>3</v>
+        <v>143</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -3351,17 +3351,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the sink 1</t>
+          <t>transporting the workpiece to the light barrier 1</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E87" t="n">
         <v>0</v>
@@ -3385,17 +3385,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the sink 2</t>
+          <t>dropping off the workpiece at the sorting machine conveyor belt</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E88" t="n">
         <v>0</v>
@@ -3419,20 +3419,20 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>moving towards the slot 1</t>
+          <t>drilling the workpiece for 3 seconds</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>163</v>
+        <v>43</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -3453,17 +3453,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the human workstation</t>
+          <t>drilling the workpiece for 6 seconds</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>194</v>
+        <v>6</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E90" t="n">
         <v>0</v>

--- a/tables/autoencoder_per_event_metrics.xlsx
+++ b/tables/autoencoder_per_event_metrics.xlsx
@@ -461,14 +461,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 24 seconds</t>
+          <t>dropping off the workpiece at the oven</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -495,11 +495,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 15 seconds</t>
+          <t>drilling the workpiece for 20 seconds</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
@@ -529,14 +529,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the oven</t>
+          <t>moving towards the slot 8</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -563,14 +563,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>lowering the workpiece</t>
+          <t>milling the workpiece</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>38</v>
+        <v>106</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -597,14 +597,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>milling the workpiece</t>
+          <t>moving towards the slot 3</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -631,11 +631,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 20 seconds</t>
+          <t>lowering the workpiece</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
@@ -699,14 +699,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>moving towards the slot 3</t>
+          <t>drilling the workpiece for 24 seconds</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>139</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -733,11 +733,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>moving towards the slot 8</t>
+          <t>drilling the workpiece for 15 seconds</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
@@ -1141,29 +1141,29 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 4</t>
+          <t>transporting the workpiece to the mill</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>158</v>
+        <v>217</v>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1175,29 +1175,29 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the mill</t>
+          <t>transporting the bucket to the slot 4</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>217</v>
+        <v>158</v>
       </c>
       <c r="C23" t="n">
+        <v>6</v>
+      </c>
+      <c r="D23" t="n">
         <v>3</v>
       </c>
-      <c r="D23" t="n">
-        <v>1</v>
-      </c>
       <c r="E23" t="n">
         <v>1</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.857</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1447,20 +1447,20 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the high bay warehouse waiting platform</t>
+          <t>burning the workpiece for 30 seconds</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>150</v>
+        <v>256</v>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1481,29 +1481,29 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>burning the workpiece for 30 seconds</t>
+          <t>transporting the workpiece to the sink 3</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>256</v>
+        <v>77</v>
       </c>
       <c r="C32" t="n">
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1515,20 +1515,20 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the drilling machine sink</t>
+          <t>picking up the workpiece from the high bay warehouse waiting platform</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>53</v>
+        <v>150</v>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1583,29 +1583,29 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the sink 3</t>
+          <t>dropping off the workpiece at the drilling machine sink</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="C35" t="n">
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
           <t>0.500</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>1.000</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1889,29 +1889,29 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the dm_2_sink</t>
+          <t>transporting the bucket to the slot 5</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C44" t="n">
         <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.400</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -1957,29 +1957,29 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 5</t>
+          <t>transporting the workpiece to the dm_2_sink</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C46" t="n">
         <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2127,20 +2127,20 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the human workstation</t>
+          <t>picking up the workpiece from the drilling machine sink</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>53</v>
+        <v>296</v>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -2195,29 +2195,29 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the drilling machine sink</t>
+          <t>transporting the workpiece to the ejection position</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>296</v>
+        <v>110</v>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2229,11 +2229,11 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the ejection position</t>
+          <t>transporting the workpiece to the sink 2</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="C54" t="n">
         <v>1</v>
@@ -2263,29 +2263,29 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the sink 2</t>
+          <t>dropping off the workpiece at the human workstation</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C55" t="n">
         <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2535,29 +2535,29 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>transporting the bucket to the vacuum gripper robot crane jib</t>
+          <t>moving towards the sink 2</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
       <c r="C63" t="n">
         <v>6</v>
       </c>
       <c r="D63" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>0.231</t>
+          <t>0.240</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2569,29 +2569,29 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>moving towards the sink 2</t>
+          <t>transporting the bucket to the vacuum gripper robot crane jib</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>244</v>
+        <v>270</v>
       </c>
       <c r="C64" t="n">
         <v>6</v>
       </c>
       <c r="D64" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>0.240</t>
+          <t>0.231</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.857</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2807,17 +2807,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>moving towards the slot 5</t>
+          <t>ejecting the workpiece to the sink 1</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>71</v>
+        <v>4</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E71" t="n">
         <v>0</v>
@@ -2841,17 +2841,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ejecting the workpiece to the sink 3</t>
+          <t>drilling the workpiece for 3 seconds</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E72" t="n">
         <v>0</v>
@@ -2875,20 +2875,20 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ejecting the workpiece to the sink 1</t>
+          <t>picking up the workpiece from the punching machine sink</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>4</v>
+        <v>83</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -2909,17 +2909,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the sink 3</t>
+          <t>moving towards the punching machine sink</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E74" t="n">
         <v>0</v>
@@ -2943,20 +2943,20 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>moving towards the slot 1</t>
+          <t>transporting the workpiece to the light barrier 1</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>163</v>
+        <v>14</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -2977,20 +2977,20 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the punching machine sink</t>
+          <t>moving towards the slot 6</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -3011,20 +3011,20 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the initial position</t>
+          <t>picking up the workpiece from the sink 2</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -3045,11 +3045,11 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>moving towards the slot 6</t>
+          <t>transporting the workpiece to the initial position</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
@@ -3058,7 +3058,7 @@
         <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -3079,20 +3079,20 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>moving towards the punching machine sink</t>
+          <t>moving towards the slot 1</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>3</v>
+        <v>163</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -3113,11 +3113,11 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the sorting machine conveyor belt</t>
+          <t>drilling the workpiece for 6 seconds</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
@@ -3126,7 +3126,7 @@
         <v>6</v>
       </c>
       <c r="E80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -3147,17 +3147,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the human workstation</t>
+          <t>moving towards the slot 5</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>194</v>
+        <v>71</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E81" t="n">
         <v>0</v>
@@ -3215,20 +3215,20 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the sink 1</t>
+          <t>transporting the bucket to the slot 7</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>6</v>
+        <v>143</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -3283,17 +3283,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>picking up the workpiece from the sink 2</t>
+          <t>picking up the workpiece from the sink 3</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E85" t="n">
         <v>0</v>
@@ -3317,20 +3317,20 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>transporting the bucket to the slot 7</t>
+          <t>ejecting the workpiece to the sink 3</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>143</v>
+        <v>29</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -3351,17 +3351,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>transporting the workpiece to the light barrier 1</t>
+          <t>dropping off the workpiece at the sorting machine conveyor belt</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E87" t="n">
         <v>0</v>
@@ -3385,17 +3385,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>dropping off the workpiece at the sorting machine conveyor belt</t>
+          <t>picking up the workpiece from the sink 1</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E88" t="n">
         <v>0</v>
@@ -3419,11 +3419,11 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 3 seconds</t>
+          <t>picking up the workpiece from the human workstation</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>43</v>
+        <v>194</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
@@ -3453,11 +3453,11 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>drilling the workpiece for 6 seconds</t>
+          <t>transporting the workpiece to the sorting machine conveyor belt</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
@@ -3466,7 +3466,7 @@
         <v>6</v>
       </c>
       <c r="E90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
